--- a/workbook/tutoring-financial-model.xlsx
+++ b/workbook/tutoring-financial-model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\tutoring-financial-model\workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5F98863-97A7-4BFD-A9BA-251961465D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E2C88F-12A6-49E3-B033-305BA3677B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="250">
   <si>
     <t>Tutoring Business Financial Model</t>
   </si>
@@ -773,12 +773,6 @@
   </si>
   <si>
     <t>Net income (annualised, $)</t>
-  </si>
-  <si>
-    <t>Selected scenario (Assumptions!scenario_switch)</t>
-  </si>
-  <si>
-    <t>Selected scenario net income ($)</t>
   </si>
   <si>
     <t>Sensitivity: net income by rate × utilisation</t>
@@ -10262,7 +10256,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -10448,24 +10442,6 @@
       <c r="D13" s="24">
         <f>D9-D10-D12</f>
         <v>32754.399999999994</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="B15" s="20" t="str">
-        <f>CHOOSE(Assumptions!$B$35,B4,C4,D4)</f>
-        <v>1. Base (actual)</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="25" t="s">
-        <v>245</v>
-      </c>
-      <c r="B16" s="24">
-        <f>CHOOSE(Assumptions!$B$35,B13,C13,D13)</f>
-        <v>30682.400000000001</v>
       </c>
     </row>
   </sheetData>
@@ -10489,7 +10465,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="34" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
@@ -10500,7 +10476,7 @@
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
@@ -10511,7 +10487,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="27" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B4" s="19">
         <f>'P&amp;L and provisioning'!$B$15</f>
@@ -10520,7 +10496,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="27" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B5" s="19">
         <f>ABS('P&amp;L and provisioning'!$B$16)</f>
@@ -10529,7 +10505,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="28">
@@ -10550,7 +10526,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="38" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B8" s="29">
         <v>0.8</v>

--- a/workbook/tutoring-financial-model.xlsx
+++ b/workbook/tutoring-financial-model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\tutoring-financial-model\workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E2C88F-12A6-49E3-B033-305BA3677B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F36971A-E7E4-4E37-A7D4-B09677DDA6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="251">
   <si>
     <t>Tutoring Business Financial Model</t>
   </si>
@@ -727,7 +727,10 @@
     <t>Annualised run-rate (extrapolated, NOT an actual full-year figure; the business wound up ~18 Sept 2026)</t>
   </si>
   <si>
-    <t>Annualisation factor (working weeks/yr ÷ weeks/term)</t>
+    <t>Annualisation factor</t>
+  </si>
+  <si>
+    <t>Working weeks/yr ÷ weeks/term.</t>
   </si>
   <si>
     <t>Net income (annualised)</t>
@@ -913,7 +916,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -950,9 +953,6 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1321,10 +1321,10 @@
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="31"/>
+      <c r="B8" s="30"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -1377,10 +1377,10 @@
       </c>
     </row>
     <row r="21" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="31"/>
+      <c r="B21" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1427,12 +1427,12 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
@@ -1478,12 +1478,12 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
@@ -1514,12 +1514,12 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
@@ -1608,12 +1608,12 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="32" t="s">
+      <c r="A23" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="31"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
     </row>
     <row r="24" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
@@ -1746,12 +1746,12 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="32" t="s">
+      <c r="A34" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="B34" s="31"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
     </row>
     <row r="35" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
@@ -1833,22 +1833,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -7547,14 +7547,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="33" t="s">
         <v>182</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
     </row>
     <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
@@ -8546,28 +8546,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
     </row>
     <row r="4" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
@@ -9920,18 +9920,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
     </row>
     <row r="2" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="32" t="s">
         <v>199</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
@@ -10079,18 +10079,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="33" t="s">
         <v>217</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="34" t="s">
         <v>218</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="37"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="36"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
@@ -10165,21 +10165,23 @@
       <c r="C10" s="9"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="35" t="s">
+      <c r="A13" s="34" t="s">
         <v>227</v>
       </c>
-      <c r="B13" s="36"/>
-      <c r="C13" s="37"/>
-    </row>
-    <row r="14" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="26" t="s">
+      <c r="B13" s="35"/>
+      <c r="C13" s="36"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
         <v>228</v>
       </c>
       <c r="B14" s="14">
         <f>Assumptions!$B$18/Assumptions!$B$17</f>
         <v>4</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="9" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
@@ -10237,7 +10239,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="21" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B21" s="24">
         <f t="shared" si="0"/>
@@ -10264,36 +10266,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
-        <v>230</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
+      <c r="A1" s="33" t="s">
+        <v>231</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
     </row>
     <row r="2" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="A2" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
     </row>
     <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B5" s="14">
         <f>Capacity!$B$10</f>
@@ -10310,7 +10312,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B6" s="7">
         <f>Assumptions!$B$7</f>
@@ -10327,7 +10329,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B7" s="24">
         <f>B5*Assumptions!$B$18*B6</f>
@@ -10344,7 +10346,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B8" s="7">
         <f>Assumptions!$B$32*Assumptions!$B$18</f>
@@ -10361,7 +10363,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="21" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B9" s="24">
         <f>B7-B8</f>
@@ -10378,7 +10380,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B10" s="7">
         <f>B9*Assumptions!$B$12</f>
@@ -10395,7 +10397,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B11" s="7">
         <f>B9-B10</f>
@@ -10412,7 +10414,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B12" s="7">
         <f>B11*Assumptions!$B$13</f>
@@ -10429,7 +10431,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B13" s="24">
         <f>B9-B10-B12</f>
@@ -10464,30 +10466,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
-        <v>244</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
+      <c r="A1" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
-        <v>245</v>
-      </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
+      <c r="A2" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="27" t="s">
-        <v>246</v>
+      <c r="A4" s="26" t="s">
+        <v>247</v>
       </c>
       <c r="B4" s="19">
         <f>'P&amp;L and provisioning'!$B$15</f>
@@ -10495,8 +10497,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
-        <v>247</v>
+      <c r="A5" s="26" t="s">
+        <v>248</v>
       </c>
       <c r="B5" s="19">
         <f>ABS('P&amp;L and provisioning'!$B$16)</f>
@@ -10505,30 +10507,30 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B7" s="5"/>
-      <c r="C7" s="28">
+      <c r="C7" s="27">
         <v>0.9</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="27">
         <v>0.95</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="27">
         <v>1</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="27">
         <v>1.05</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="27">
         <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="38" t="s">
-        <v>249</v>
-      </c>
-      <c r="B8" s="29">
+      <c r="A8" s="37" t="s">
+        <v>250</v>
+      </c>
+      <c r="B8" s="28">
         <v>0.8</v>
       </c>
       <c r="C8" s="7">
@@ -10553,8 +10555,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="31"/>
-      <c r="B9" s="29">
+      <c r="A9" s="30"/>
+      <c r="B9" s="28">
         <v>0.9</v>
       </c>
       <c r="C9" s="7">
@@ -10579,8 +10581,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="31"/>
-      <c r="B10" s="29">
+      <c r="A10" s="30"/>
+      <c r="B10" s="28">
         <v>1</v>
       </c>
       <c r="C10" s="7">
@@ -10605,8 +10607,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="31"/>
-      <c r="B11" s="29">
+      <c r="A11" s="30"/>
+      <c r="B11" s="28">
         <v>1.1000000000000001</v>
       </c>
       <c r="C11" s="7">
@@ -10631,8 +10633,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="31"/>
-      <c r="B12" s="29">
+      <c r="A12" s="30"/>
+      <c r="B12" s="28">
         <v>1.2</v>
       </c>
       <c r="C12" s="7">

--- a/workbook/tutoring-financial-model.xlsx
+++ b/workbook/tutoring-financial-model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\tutoring-financial-model\workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F36971A-E7E4-4E37-A7D4-B09677DDA6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426B7F9A-F5FC-43CD-95FD-456ED8511B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,8 +40,32 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Model</author>
+  </authors>
+  <commentList>
+    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Working weeks/yr ÷ weeks/term.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="250">
   <si>
     <t>Tutoring Business Financial Model</t>
   </si>
@@ -724,13 +748,10 @@
     <t>Net income (period)</t>
   </si>
   <si>
-    <t>Annualised run-rate (extrapolated, NOT an actual full-year figure; the business wound up ~18 Sept 2026)</t>
+    <t>Annualised run-rate</t>
   </si>
   <si>
     <t>Annualisation factor</t>
-  </si>
-  <si>
-    <t>Working weeks/yr ÷ weeks/term.</t>
   </si>
   <si>
     <t>Net income (annualised)</t>
@@ -972,8 +993,8 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -10069,8 +10090,8 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:C21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -10089,8 +10110,8 @@
       <c r="A3" s="34" t="s">
         <v>218</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="36"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="35"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
@@ -10164,12 +10185,11 @@
       </c>
       <c r="C10" s="9"/>
     </row>
-    <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="34" t="s">
         <v>227</v>
       </c>
       <c r="B13" s="35"/>
-      <c r="C13" s="36"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
@@ -10179,9 +10199,6 @@
         <f>Assumptions!$B$18/Assumptions!$B$17</f>
         <v>4</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>229</v>
-      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
@@ -10239,20 +10256,28 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B21" s="24">
         <f t="shared" si="0"/>
         <v>30682.400000000001</v>
       </c>
     </row>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="32" t="s">
+        <v>216</v>
+      </c>
+      <c r="B23" s="30"/>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A23:B23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10267,7 +10292,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="33" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -10275,7 +10300,7 @@
     </row>
     <row r="2" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -10284,18 +10309,18 @@
     <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>234</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B5" s="14">
         <f>Capacity!$B$10</f>
@@ -10312,7 +10337,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B6" s="7">
         <f>Assumptions!$B$7</f>
@@ -10329,7 +10354,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B7" s="24">
         <f>B5*Assumptions!$B$18*B6</f>
@@ -10346,7 +10371,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B8" s="7">
         <f>Assumptions!$B$32*Assumptions!$B$18</f>
@@ -10363,7 +10388,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="21" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B9" s="24">
         <f>B7-B8</f>
@@ -10380,7 +10405,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B10" s="7">
         <f>B9*Assumptions!$B$12</f>
@@ -10397,7 +10422,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B11" s="7">
         <f>B9-B10</f>
@@ -10414,7 +10439,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B12" s="7">
         <f>B11*Assumptions!$B$13</f>
@@ -10431,7 +10456,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B13" s="24">
         <f>B9-B10-B12</f>
@@ -10467,7 +10492,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="33" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -10478,7 +10503,7 @@
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="32" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
@@ -10489,7 +10514,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B4" s="19">
         <f>'P&amp;L and provisioning'!$B$15</f>
@@ -10498,7 +10523,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="26" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B5" s="19">
         <f>ABS('P&amp;L and provisioning'!$B$16)</f>
@@ -10507,7 +10532,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="27">
@@ -10528,7 +10553,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="37" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B8" s="28">
         <v>0.8</v>

--- a/workbook/tutoring-financial-model.xlsx
+++ b/workbook/tutoring-financial-model.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\tutoring-financial-model\workbook\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Projects\tutoring-financial-model\workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426B7F9A-F5FC-43CD-95FD-456ED8511B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9B97E7C-5C6E-417C-A211-A85A847CD26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -840,40 +840,42 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF2D3142"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
       <b/>
-      <sz val="14"/>
-      <name val="Calibri"/>
+      <sz val="15"/>
+      <color rgb="FF2D3142"/>
+      <name val="Segoe UI"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <color rgb="FF2D3142"/>
+      <name val="Segoe UI"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <color rgb="FF4F5D75"/>
+      <name val="Segoe UI"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="Segoe UI"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <color rgb="FFEB6C36"/>
+      <name val="Segoe UI"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -882,7 +884,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
+        <fgColor rgb="FF2D3142"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEEF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFE9"/>
       </patternFill>
     </fill>
   </fills>
@@ -896,16 +908,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFD8DAE0"/>
       </left>
       <right style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFD8DAE0"/>
       </right>
       <top style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFD8DAE0"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFD8DAE0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -913,23 +925,23 @@
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFD8DAE0"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFD8DAE0"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFD8DAE0"/>
       </right>
       <top style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFD8DAE0"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFD8DAE0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -937,65 +949,67 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1307,101 +1321,101 @@
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="4" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:2" ht="50.4" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="30"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="B8" s="32"/>
+    </row>
+    <row r="10" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="11" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="12" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="13" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="14" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="15" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="16" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="17" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="18" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A20" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="30"/>
+      <c r="B21" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1423,410 +1437,410 @@
     <col min="4" max="4" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:4" ht="67.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:4" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="31" t="s">
+    <row r="6" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A6" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-    </row>
-    <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+    </row>
+    <row r="7" spans="1:4" ht="33.6" x14ac:dyDescent="0.4">
+      <c r="A7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="7">
-        <v>40</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="8">
+        <v>40</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="10" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="10">
-        <v>30</v>
-      </c>
-      <c r="C8" s="8" t="s">
+    <row r="8" spans="1:4" ht="33.6" x14ac:dyDescent="0.4">
+      <c r="A8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="11">
+        <v>30</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A9" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="8">
         <f>$B$7/($B$8/60)</f>
         <v>80</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="31" t="s">
+    <row r="11" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A11" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+      <c r="B11" s="32"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+    </row>
+    <row r="12" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A12" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="12">
         <v>0.125</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="11">
+    <row r="13" spans="1:4" ht="67.2" x14ac:dyDescent="0.4">
+      <c r="A13" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="12">
         <v>0.2</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="10" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="31" t="s">
+    <row r="15" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A15" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+    </row>
+    <row r="16" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A16" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="11">
         <v>4</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="10" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
+    <row r="17" spans="1:4" ht="33.6" x14ac:dyDescent="0.4">
+      <c r="A17" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="11">
         <v>9</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+    <row r="18" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A18" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="11">
         <f>$B$16*$B$17</f>
         <v>36</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
+    <row r="19" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A19" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="11">
         <v>5</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="10" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
+    <row r="20" spans="1:4" ht="67.2" x14ac:dyDescent="0.4">
+      <c r="A20" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="11">
         <v>37</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="10" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:4" ht="50.4" x14ac:dyDescent="0.4">
+      <c r="A21" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="13">
         <f>$B$20*$B$8/60</f>
         <v>18.5</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="10" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="31" t="s">
+    <row r="23" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A23" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-    </row>
-    <row r="24" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+    </row>
+    <row r="24" spans="1:4" ht="33.6" x14ac:dyDescent="0.4">
+      <c r="A24" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="13">
         <v>1.5</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="10" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
+    <row r="25" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A25" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="13">
         <f>$B$24*$B$19</f>
         <v>7.5</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
+    <row r="26" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A26" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="8">
         <v>150</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="10" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
+    <row r="27" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A27" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="14">
         <v>1.8</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
+    <row r="28" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A28" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B28" s="12">
-        <v>40</v>
-      </c>
-      <c r="C28" s="8" t="s">
+      <c r="B28" s="13">
+        <v>40</v>
+      </c>
+      <c r="C28" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="10" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
+    <row r="29" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A29" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="13">
         <v>1.5</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="10" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="6" t="s">
+    <row r="30" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A30" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="8">
         <f>$B$26*12/$B$18</f>
         <v>50</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="6" t="s">
+    <row r="31" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A31" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="8">
         <f>$B$28*$B$27/$B$29</f>
         <v>48</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="10" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="6" t="s">
+    <row r="32" spans="1:4" ht="33.6" x14ac:dyDescent="0.4">
+      <c r="A32" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="8">
         <f>$B$30+$B$31</f>
         <v>98</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="D32" s="10" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="31" t="s">
+    <row r="34" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A34" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-    </row>
-    <row r="35" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
+      <c r="B34" s="32"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+    </row>
+    <row r="35" spans="1:4" ht="50.4" x14ac:dyDescent="0.4">
+      <c r="A35" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="11">
         <v>1</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="D35" s="10" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
+    <row r="36" spans="1:4" ht="33.6" x14ac:dyDescent="0.4">
+      <c r="A36" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="B36" s="14">
+      <c r="B36" s="15">
         <v>1.3</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="D36" s="10" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="6" t="s">
+    <row r="37" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A37" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="B37" s="14">
+      <c r="B37" s="15">
         <v>1.25</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="10" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="6" t="s">
+    <row r="38" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A38" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B38" s="14">
+      <c r="B38" s="15">
         <v>0.85</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="D38" s="9" t="s">
+      <c r="D38" s="10" t="s">
         <v>90</v>
       </c>
     </row>
@@ -1853,43 +1867,43 @@
     <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:5" ht="23.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+    </row>
+    <row r="4" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+    <row r="5" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B5" s="16" t="s">
@@ -1905,8 +1919,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+    <row r="6" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A6" s="2" t="s">
         <v>101</v>
       </c>
       <c r="B6" s="16" t="s">
@@ -1922,8 +1936,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+    <row r="7" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B7" s="16" t="s">
@@ -1939,8 +1953,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+    <row r="8" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
         <v>103</v>
       </c>
       <c r="B8" s="16" t="s">
@@ -1956,8 +1970,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+    <row r="9" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B9" s="16" t="s">
@@ -1973,8 +1987,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+    <row r="10" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A10" s="2" t="s">
         <v>105</v>
       </c>
       <c r="B10" s="16" t="s">
@@ -1990,8 +2004,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+    <row r="11" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B11" s="16" t="s">
@@ -2007,8 +2021,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+    <row r="12" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
         <v>107</v>
       </c>
       <c r="B12" s="16" t="s">
@@ -2024,8 +2038,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+    <row r="13" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B13" s="16" t="s">
@@ -2041,8 +2055,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
+    <row r="14" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B14" s="16" t="s">
@@ -2058,8 +2072,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="15" t="s">
+    <row r="15" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
         <v>111</v>
       </c>
       <c r="B15" s="16" t="s">
@@ -2075,8 +2089,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="15" t="s">
+    <row r="16" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A16" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B16" s="16" t="s">
@@ -2092,8 +2106,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="15" t="s">
+    <row r="17" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A17" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B17" s="16" t="s">
@@ -2109,8 +2123,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
+    <row r="18" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A18" s="2" t="s">
         <v>115</v>
       </c>
       <c r="B18" s="16" t="s">
@@ -2126,8 +2140,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
+    <row r="19" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A19" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B19" s="16" t="s">
@@ -2143,8 +2157,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="15" t="s">
+    <row r="20" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A20" s="2" t="s">
         <v>118</v>
       </c>
       <c r="B20" s="16" t="s">
@@ -2160,8 +2174,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="15" t="s">
+    <row r="21" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A21" s="2" t="s">
         <v>119</v>
       </c>
       <c r="B21" s="16" t="s">
@@ -2177,8 +2191,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="15" t="s">
+    <row r="22" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A22" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B22" s="16" t="s">
@@ -2194,8 +2208,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="15" t="s">
+    <row r="23" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A23" s="2" t="s">
         <v>121</v>
       </c>
       <c r="B23" s="16" t="s">
@@ -2211,8 +2225,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="15" t="s">
+    <row r="24" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A24" s="2" t="s">
         <v>122</v>
       </c>
       <c r="B24" s="16" t="s">
@@ -2228,8 +2242,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="15" t="s">
+    <row r="25" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A25" s="2" t="s">
         <v>123</v>
       </c>
       <c r="B25" s="16" t="s">
@@ -2245,8 +2259,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="15" t="s">
+    <row r="26" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A26" s="2" t="s">
         <v>124</v>
       </c>
       <c r="B26" s="16" t="s">
@@ -2262,8 +2276,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="15" t="s">
+    <row r="27" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A27" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B27" s="16" t="s">
@@ -2279,8 +2293,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="15" t="s">
+    <row r="28" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A28" s="2" t="s">
         <v>127</v>
       </c>
       <c r="B28" s="16" t="s">
@@ -2296,8 +2310,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="15" t="s">
+    <row r="29" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A29" s="2" t="s">
         <v>128</v>
       </c>
       <c r="B29" s="16" t="s">
@@ -2313,8 +2327,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="15" t="s">
+    <row r="30" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A30" s="2" t="s">
         <v>129</v>
       </c>
       <c r="B30" s="16" t="s">
@@ -2330,8 +2344,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="15" t="s">
+    <row r="31" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A31" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B31" s="16" t="s">
@@ -2347,8 +2361,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="15" t="s">
+    <row r="32" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A32" s="2" t="s">
         <v>131</v>
       </c>
       <c r="B32" s="16" t="s">
@@ -2364,8 +2378,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="15" t="s">
+    <row r="33" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A33" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B33" s="16" t="s">
@@ -2381,8 +2395,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="15" t="s">
+    <row r="34" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A34" s="2" t="s">
         <v>133</v>
       </c>
       <c r="B34" s="16" t="s">
@@ -2398,8 +2412,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="15" t="s">
+    <row r="35" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A35" s="2" t="s">
         <v>135</v>
       </c>
       <c r="B35" s="16" t="s">
@@ -2415,8 +2429,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="15" t="s">
+    <row r="36" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A36" s="2" t="s">
         <v>136</v>
       </c>
       <c r="B36" s="16" t="s">
@@ -2432,8 +2446,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="15" t="s">
+    <row r="37" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A37" s="2" t="s">
         <v>137</v>
       </c>
       <c r="B37" s="16" t="s">
@@ -2449,8 +2463,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="15" t="s">
+    <row r="38" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A38" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B38" s="16" t="s">
@@ -2466,8 +2480,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="15" t="s">
+    <row r="39" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A39" s="2" t="s">
         <v>139</v>
       </c>
       <c r="B39" s="16" t="s">
@@ -2483,8 +2497,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="15" t="s">
+    <row r="40" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A40" s="2" t="s">
         <v>140</v>
       </c>
       <c r="B40" s="16" t="s">
@@ -2500,8 +2514,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="15" t="s">
+    <row r="41" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A41" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B41" s="16" t="s">
@@ -2517,8 +2531,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="15" t="s">
+    <row r="42" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A42" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B42" s="16" t="s">
@@ -2534,8 +2548,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="15" t="s">
+    <row r="43" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A43" s="2" t="s">
         <v>101</v>
       </c>
       <c r="B43" s="16" t="s">
@@ -2551,8 +2565,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="15" t="s">
+    <row r="44" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A44" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B44" s="16" t="s">
@@ -2568,8 +2582,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="15" t="s">
+    <row r="45" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A45" s="2" t="s">
         <v>103</v>
       </c>
       <c r="B45" s="16" t="s">
@@ -2585,8 +2599,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="15" t="s">
+    <row r="46" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A46" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B46" s="16" t="s">
@@ -2602,8 +2616,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="15" t="s">
+    <row r="47" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A47" s="2" t="s">
         <v>105</v>
       </c>
       <c r="B47" s="16" t="s">
@@ -2619,8 +2633,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="15" t="s">
+    <row r="48" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A48" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B48" s="16" t="s">
@@ -2636,8 +2650,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="15" t="s">
+    <row r="49" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A49" s="2" t="s">
         <v>107</v>
       </c>
       <c r="B49" s="16" t="s">
@@ -2653,8 +2667,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="15" t="s">
+    <row r="50" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A50" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B50" s="16" t="s">
@@ -2670,8 +2684,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="15" t="s">
+    <row r="51" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A51" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B51" s="16" t="s">
@@ -2687,8 +2701,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="15" t="s">
+    <row r="52" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A52" s="2" t="s">
         <v>111</v>
       </c>
       <c r="B52" s="16" t="s">
@@ -2704,8 +2718,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="15" t="s">
+    <row r="53" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A53" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B53" s="16" t="s">
@@ -2721,8 +2735,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="15" t="s">
+    <row r="54" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A54" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B54" s="16" t="s">
@@ -2738,8 +2752,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="15" t="s">
+    <row r="55" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A55" s="2" t="s">
         <v>115</v>
       </c>
       <c r="B55" s="16" t="s">
@@ -2755,8 +2769,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="15" t="s">
+    <row r="56" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A56" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B56" s="16" t="s">
@@ -2772,8 +2786,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="15" t="s">
+    <row r="57" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A57" s="2" t="s">
         <v>118</v>
       </c>
       <c r="B57" s="16" t="s">
@@ -2789,8 +2803,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="15" t="s">
+    <row r="58" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A58" s="2" t="s">
         <v>119</v>
       </c>
       <c r="B58" s="16" t="s">
@@ -2806,8 +2820,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="15" t="s">
+    <row r="59" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A59" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B59" s="16" t="s">
@@ -2823,8 +2837,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="15" t="s">
+    <row r="60" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A60" s="2" t="s">
         <v>121</v>
       </c>
       <c r="B60" s="16" t="s">
@@ -2840,8 +2854,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="15" t="s">
+    <row r="61" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A61" s="2" t="s">
         <v>122</v>
       </c>
       <c r="B61" s="16" t="s">
@@ -2857,8 +2871,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="15" t="s">
+    <row r="62" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A62" s="2" t="s">
         <v>123</v>
       </c>
       <c r="B62" s="16" t="s">
@@ -2874,8 +2888,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="15" t="s">
+    <row r="63" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A63" s="2" t="s">
         <v>124</v>
       </c>
       <c r="B63" s="16" t="s">
@@ -2891,8 +2905,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="15" t="s">
+    <row r="64" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A64" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B64" s="16" t="s">
@@ -2908,8 +2922,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" s="15" t="s">
+    <row r="65" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A65" s="2" t="s">
         <v>127</v>
       </c>
       <c r="B65" s="16" t="s">
@@ -2925,8 +2939,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" s="15" t="s">
+    <row r="66" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A66" s="2" t="s">
         <v>128</v>
       </c>
       <c r="B66" s="16" t="s">
@@ -2942,8 +2956,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="15" t="s">
+    <row r="67" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A67" s="2" t="s">
         <v>129</v>
       </c>
       <c r="B67" s="16" t="s">
@@ -2959,8 +2973,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="15" t="s">
+    <row r="68" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A68" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B68" s="16" t="s">
@@ -2976,8 +2990,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="15" t="s">
+    <row r="69" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A69" s="2" t="s">
         <v>131</v>
       </c>
       <c r="B69" s="16" t="s">
@@ -2993,8 +3007,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" s="15" t="s">
+    <row r="70" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A70" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B70" s="16" t="s">
@@ -3010,8 +3024,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" s="15" t="s">
+    <row r="71" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A71" s="2" t="s">
         <v>133</v>
       </c>
       <c r="B71" s="16" t="s">
@@ -3027,8 +3041,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" s="15" t="s">
+    <row r="72" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A72" s="2" t="s">
         <v>135</v>
       </c>
       <c r="B72" s="16" t="s">
@@ -3044,8 +3058,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="15" t="s">
+    <row r="73" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A73" s="2" t="s">
         <v>136</v>
       </c>
       <c r="B73" s="16" t="s">
@@ -3061,8 +3075,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="15" t="s">
+    <row r="74" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A74" s="2" t="s">
         <v>137</v>
       </c>
       <c r="B74" s="16" t="s">
@@ -3078,8 +3092,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="15" t="s">
+    <row r="75" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A75" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B75" s="16" t="s">
@@ -3095,8 +3109,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" s="15" t="s">
+    <row r="76" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A76" s="2" t="s">
         <v>139</v>
       </c>
       <c r="B76" s="16" t="s">
@@ -3112,8 +3126,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" s="15" t="s">
+    <row r="77" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A77" s="2" t="s">
         <v>140</v>
       </c>
       <c r="B77" s="16" t="s">
@@ -3129,8 +3143,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" s="15" t="s">
+    <row r="78" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A78" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B78" s="16" t="s">
@@ -3146,8 +3160,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" s="15" t="s">
+    <row r="79" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A79" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B79" s="16" t="s">
@@ -3163,8 +3177,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="15" t="s">
+    <row r="80" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A80" s="2" t="s">
         <v>101</v>
       </c>
       <c r="B80" s="16" t="s">
@@ -3180,8 +3194,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="15" t="s">
+    <row r="81" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A81" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B81" s="16" t="s">
@@ -3197,8 +3211,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" s="15" t="s">
+    <row r="82" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A82" s="2" t="s">
         <v>103</v>
       </c>
       <c r="B82" s="16" t="s">
@@ -3214,8 +3228,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83" s="15" t="s">
+    <row r="83" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A83" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B83" s="16" t="s">
@@ -3231,8 +3245,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84" s="15" t="s">
+    <row r="84" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A84" s="2" t="s">
         <v>105</v>
       </c>
       <c r="B84" s="16" t="s">
@@ -3248,8 +3262,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" s="15" t="s">
+    <row r="85" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A85" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B85" s="16" t="s">
@@ -3265,8 +3279,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86" s="15" t="s">
+    <row r="86" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A86" s="2" t="s">
         <v>107</v>
       </c>
       <c r="B86" s="16" t="s">
@@ -3282,8 +3296,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87" s="15" t="s">
+    <row r="87" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A87" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B87" s="16" t="s">
@@ -3299,8 +3313,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" s="15" t="s">
+    <row r="88" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A88" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B88" s="16" t="s">
@@ -3316,8 +3330,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89" s="15" t="s">
+    <row r="89" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A89" s="2" t="s">
         <v>111</v>
       </c>
       <c r="B89" s="16" t="s">
@@ -3333,8 +3347,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A90" s="15" t="s">
+    <row r="90" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A90" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B90" s="16" t="s">
@@ -3350,8 +3364,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A91" s="15" t="s">
+    <row r="91" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A91" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B91" s="16" t="s">
@@ -3367,8 +3381,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" s="15" t="s">
+    <row r="92" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A92" s="2" t="s">
         <v>115</v>
       </c>
       <c r="B92" s="16" t="s">
@@ -3384,8 +3398,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" s="15" t="s">
+    <row r="93" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A93" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B93" s="16" t="s">
@@ -3401,8 +3415,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" s="15" t="s">
+    <row r="94" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A94" s="2" t="s">
         <v>118</v>
       </c>
       <c r="B94" s="16" t="s">
@@ -3418,8 +3432,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="15" t="s">
+    <row r="95" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A95" s="2" t="s">
         <v>119</v>
       </c>
       <c r="B95" s="16" t="s">
@@ -3435,8 +3449,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96" s="15" t="s">
+    <row r="96" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A96" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B96" s="16" t="s">
@@ -3452,8 +3466,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="15" t="s">
+    <row r="97" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A97" s="2" t="s">
         <v>121</v>
       </c>
       <c r="B97" s="16" t="s">
@@ -3469,8 +3483,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="15" t="s">
+    <row r="98" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A98" s="2" t="s">
         <v>122</v>
       </c>
       <c r="B98" s="16" t="s">
@@ -3486,8 +3500,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="15" t="s">
+    <row r="99" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A99" s="2" t="s">
         <v>123</v>
       </c>
       <c r="B99" s="16" t="s">
@@ -3503,8 +3517,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="15" t="s">
+    <row r="100" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A100" s="2" t="s">
         <v>124</v>
       </c>
       <c r="B100" s="16" t="s">
@@ -3520,8 +3534,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101" s="15" t="s">
+    <row r="101" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A101" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B101" s="16" t="s">
@@ -3537,8 +3551,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A102" s="15" t="s">
+    <row r="102" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A102" s="2" t="s">
         <v>127</v>
       </c>
       <c r="B102" s="16" t="s">
@@ -3554,8 +3568,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103" s="15" t="s">
+    <row r="103" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A103" s="2" t="s">
         <v>128</v>
       </c>
       <c r="B103" s="16" t="s">
@@ -3571,8 +3585,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104" s="15" t="s">
+    <row r="104" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A104" s="2" t="s">
         <v>129</v>
       </c>
       <c r="B104" s="16" t="s">
@@ -3588,8 +3602,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A105" s="15" t="s">
+    <row r="105" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A105" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B105" s="16" t="s">
@@ -3605,8 +3619,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A106" s="15" t="s">
+    <row r="106" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A106" s="2" t="s">
         <v>131</v>
       </c>
       <c r="B106" s="16" t="s">
@@ -3622,8 +3636,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107" s="15" t="s">
+    <row r="107" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A107" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B107" s="16" t="s">
@@ -3639,8 +3653,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" s="15" t="s">
+    <row r="108" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A108" s="2" t="s">
         <v>124</v>
       </c>
       <c r="B108" s="16" t="s">
@@ -3656,8 +3670,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="15" t="s">
+    <row r="109" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A109" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B109" s="16" t="s">
@@ -3673,8 +3687,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A110" s="15" t="s">
+    <row r="110" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A110" s="2" t="s">
         <v>127</v>
       </c>
       <c r="B110" s="16" t="s">
@@ -3690,8 +3704,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A111" s="15" t="s">
+    <row r="111" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A111" s="2" t="s">
         <v>128</v>
       </c>
       <c r="B111" s="16" t="s">
@@ -3707,8 +3721,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" s="15" t="s">
+    <row r="112" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A112" s="2" t="s">
         <v>129</v>
       </c>
       <c r="B112" s="16" t="s">
@@ -3724,8 +3738,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" s="15" t="s">
+    <row r="113" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A113" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B113" s="16" t="s">
@@ -3741,8 +3755,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A114" s="15" t="s">
+    <row r="114" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A114" s="2" t="s">
         <v>131</v>
       </c>
       <c r="B114" s="16" t="s">
@@ -3758,8 +3772,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A115" s="15" t="s">
+    <row r="115" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A115" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B115" s="16" t="s">
@@ -3775,8 +3789,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A116" s="15" t="s">
+    <row r="116" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A116" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B116" s="16" t="s">
@@ -3792,8 +3806,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A117" s="15" t="s">
+    <row r="117" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A117" s="2" t="s">
         <v>101</v>
       </c>
       <c r="B117" s="16" t="s">
@@ -3809,8 +3823,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A118" s="15" t="s">
+    <row r="118" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A118" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B118" s="16" t="s">
@@ -3826,8 +3840,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A119" s="15" t="s">
+    <row r="119" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A119" s="2" t="s">
         <v>103</v>
       </c>
       <c r="B119" s="16" t="s">
@@ -3843,8 +3857,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A120" s="15" t="s">
+    <row r="120" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A120" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B120" s="16" t="s">
@@ -3860,8 +3874,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A121" s="15" t="s">
+    <row r="121" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A121" s="2" t="s">
         <v>105</v>
       </c>
       <c r="B121" s="16" t="s">
@@ -3877,8 +3891,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A122" s="15" t="s">
+    <row r="122" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A122" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B122" s="16" t="s">
@@ -3894,8 +3908,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A123" s="15" t="s">
+    <row r="123" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A123" s="2" t="s">
         <v>107</v>
       </c>
       <c r="B123" s="16" t="s">
@@ -3911,8 +3925,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A124" s="15" t="s">
+    <row r="124" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A124" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B124" s="16" t="s">
@@ -3928,8 +3942,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A125" s="15" t="s">
+    <row r="125" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A125" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B125" s="16" t="s">
@@ -3945,8 +3959,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A126" s="15" t="s">
+    <row r="126" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A126" s="2" t="s">
         <v>111</v>
       </c>
       <c r="B126" s="16" t="s">
@@ -3962,8 +3976,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A127" s="15" t="s">
+    <row r="127" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A127" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B127" s="16" t="s">
@@ -3979,8 +3993,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A128" s="15" t="s">
+    <row r="128" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A128" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B128" s="16" t="s">
@@ -3996,8 +4010,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A129" s="15" t="s">
+    <row r="129" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A129" s="2" t="s">
         <v>115</v>
       </c>
       <c r="B129" s="16" t="s">
@@ -4013,8 +4027,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A130" s="15" t="s">
+    <row r="130" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A130" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B130" s="16" t="s">
@@ -4030,8 +4044,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A131" s="15" t="s">
+    <row r="131" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A131" s="2" t="s">
         <v>118</v>
       </c>
       <c r="B131" s="16" t="s">
@@ -4047,8 +4061,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A132" s="15" t="s">
+    <row r="132" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A132" s="2" t="s">
         <v>119</v>
       </c>
       <c r="B132" s="16" t="s">
@@ -4064,8 +4078,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A133" s="15" t="s">
+    <row r="133" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A133" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B133" s="16" t="s">
@@ -4081,8 +4095,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A134" s="15" t="s">
+    <row r="134" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A134" s="2" t="s">
         <v>121</v>
       </c>
       <c r="B134" s="16" t="s">
@@ -4098,8 +4112,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A135" s="15" t="s">
+    <row r="135" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A135" s="2" t="s">
         <v>122</v>
       </c>
       <c r="B135" s="16" t="s">
@@ -4115,8 +4129,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A136" s="15" t="s">
+    <row r="136" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A136" s="2" t="s">
         <v>123</v>
       </c>
       <c r="B136" s="16" t="s">
@@ -4132,8 +4146,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A137" s="15" t="s">
+    <row r="137" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A137" s="2" t="s">
         <v>124</v>
       </c>
       <c r="B137" s="16" t="s">
@@ -4149,8 +4163,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A138" s="15" t="s">
+    <row r="138" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A138" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B138" s="16" t="s">
@@ -4166,8 +4180,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A139" s="15" t="s">
+    <row r="139" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A139" s="2" t="s">
         <v>127</v>
       </c>
       <c r="B139" s="16" t="s">
@@ -4183,8 +4197,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A140" s="15" t="s">
+    <row r="140" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A140" s="2" t="s">
         <v>128</v>
       </c>
       <c r="B140" s="16" t="s">
@@ -4200,8 +4214,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A141" s="15" t="s">
+    <row r="141" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A141" s="2" t="s">
         <v>129</v>
       </c>
       <c r="B141" s="16" t="s">
@@ -4217,8 +4231,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A142" s="15" t="s">
+    <row r="142" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A142" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B142" s="16" t="s">
@@ -4234,8 +4248,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A143" s="15" t="s">
+    <row r="143" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A143" s="2" t="s">
         <v>131</v>
       </c>
       <c r="B143" s="16" t="s">
@@ -4251,8 +4265,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A144" s="15" t="s">
+    <row r="144" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A144" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B144" s="16" t="s">
@@ -4268,8 +4282,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A145" s="15" t="s">
+    <row r="145" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A145" s="2" t="s">
         <v>133</v>
       </c>
       <c r="B145" s="16" t="s">
@@ -4285,8 +4299,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A146" s="15" t="s">
+    <row r="146" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A146" s="2" t="s">
         <v>135</v>
       </c>
       <c r="B146" s="16" t="s">
@@ -4302,8 +4316,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A147" s="15" t="s">
+    <row r="147" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A147" s="2" t="s">
         <v>136</v>
       </c>
       <c r="B147" s="16" t="s">
@@ -4319,8 +4333,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A148" s="15" t="s">
+    <row r="148" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A148" s="2" t="s">
         <v>137</v>
       </c>
       <c r="B148" s="16" t="s">
@@ -4336,8 +4350,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A149" s="15" t="s">
+    <row r="149" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A149" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B149" s="16" t="s">
@@ -4353,8 +4367,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A150" s="15" t="s">
+    <row r="150" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A150" s="2" t="s">
         <v>139</v>
       </c>
       <c r="B150" s="16" t="s">
@@ -4370,8 +4384,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A151" s="15" t="s">
+    <row r="151" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A151" s="2" t="s">
         <v>140</v>
       </c>
       <c r="B151" s="16" t="s">
@@ -4387,8 +4401,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A152" s="15" t="s">
+    <row r="152" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A152" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B152" s="16" t="s">
@@ -4404,8 +4418,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A153" s="15" t="s">
+    <row r="153" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A153" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B153" s="16" t="s">
@@ -4421,8 +4435,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A154" s="15" t="s">
+    <row r="154" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A154" s="2" t="s">
         <v>101</v>
       </c>
       <c r="B154" s="16" t="s">
@@ -4438,8 +4452,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A155" s="15" t="s">
+    <row r="155" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A155" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B155" s="16" t="s">
@@ -4455,8 +4469,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A156" s="15" t="s">
+    <row r="156" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A156" s="2" t="s">
         <v>103</v>
       </c>
       <c r="B156" s="16" t="s">
@@ -4472,8 +4486,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A157" s="15" t="s">
+    <row r="157" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A157" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B157" s="16" t="s">
@@ -4489,8 +4503,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A158" s="15" t="s">
+    <row r="158" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A158" s="2" t="s">
         <v>105</v>
       </c>
       <c r="B158" s="16" t="s">
@@ -4506,8 +4520,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A159" s="15" t="s">
+    <row r="159" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A159" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B159" s="16" t="s">
@@ -4523,8 +4537,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A160" s="15" t="s">
+    <row r="160" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A160" s="2" t="s">
         <v>107</v>
       </c>
       <c r="B160" s="16" t="s">
@@ -4540,8 +4554,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A161" s="15" t="s">
+    <row r="161" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A161" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B161" s="16" t="s">
@@ -4557,8 +4571,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A162" s="15" t="s">
+    <row r="162" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A162" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B162" s="16" t="s">
@@ -4574,8 +4588,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A163" s="15" t="s">
+    <row r="163" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A163" s="2" t="s">
         <v>111</v>
       </c>
       <c r="B163" s="16" t="s">
@@ -4591,8 +4605,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A164" s="15" t="s">
+    <row r="164" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A164" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B164" s="16" t="s">
@@ -4608,8 +4622,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A165" s="15" t="s">
+    <row r="165" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A165" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B165" s="16" t="s">
@@ -4625,8 +4639,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A166" s="15" t="s">
+    <row r="166" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A166" s="2" t="s">
         <v>115</v>
       </c>
       <c r="B166" s="16" t="s">
@@ -4642,8 +4656,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A167" s="15" t="s">
+    <row r="167" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A167" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B167" s="16" t="s">
@@ -4659,8 +4673,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A168" s="15" t="s">
+    <row r="168" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A168" s="2" t="s">
         <v>118</v>
       </c>
       <c r="B168" s="16" t="s">
@@ -4676,8 +4690,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A169" s="15" t="s">
+    <row r="169" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A169" s="2" t="s">
         <v>119</v>
       </c>
       <c r="B169" s="16" t="s">
@@ -4693,8 +4707,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A170" s="15" t="s">
+    <row r="170" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A170" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B170" s="16" t="s">
@@ -4710,8 +4724,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A171" s="15" t="s">
+    <row r="171" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A171" s="2" t="s">
         <v>121</v>
       </c>
       <c r="B171" s="16" t="s">
@@ -4727,8 +4741,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A172" s="15" t="s">
+    <row r="172" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A172" s="2" t="s">
         <v>122</v>
       </c>
       <c r="B172" s="16" t="s">
@@ -4744,8 +4758,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A173" s="15" t="s">
+    <row r="173" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A173" s="2" t="s">
         <v>123</v>
       </c>
       <c r="B173" s="16" t="s">
@@ -4761,8 +4775,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A174" s="15" t="s">
+    <row r="174" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A174" s="2" t="s">
         <v>124</v>
       </c>
       <c r="B174" s="16" t="s">
@@ -4778,8 +4792,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A175" s="15" t="s">
+    <row r="175" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A175" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B175" s="16" t="s">
@@ -4795,8 +4809,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A176" s="15" t="s">
+    <row r="176" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A176" s="2" t="s">
         <v>127</v>
       </c>
       <c r="B176" s="16" t="s">
@@ -4812,8 +4826,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A177" s="15" t="s">
+    <row r="177" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A177" s="2" t="s">
         <v>128</v>
       </c>
       <c r="B177" s="16" t="s">
@@ -4829,8 +4843,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A178" s="15" t="s">
+    <row r="178" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A178" s="2" t="s">
         <v>129</v>
       </c>
       <c r="B178" s="16" t="s">
@@ -4846,8 +4860,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A179" s="15" t="s">
+    <row r="179" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A179" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B179" s="16" t="s">
@@ -4863,8 +4877,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A180" s="15" t="s">
+    <row r="180" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A180" s="2" t="s">
         <v>131</v>
       </c>
       <c r="B180" s="16" t="s">
@@ -4880,8 +4894,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A181" s="15" t="s">
+    <row r="181" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A181" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B181" s="16" t="s">
@@ -4897,8 +4911,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A182" s="15" t="s">
+    <row r="182" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A182" s="2" t="s">
         <v>133</v>
       </c>
       <c r="B182" s="16" t="s">
@@ -4914,8 +4928,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A183" s="15" t="s">
+    <row r="183" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A183" s="2" t="s">
         <v>135</v>
       </c>
       <c r="B183" s="16" t="s">
@@ -4931,8 +4945,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A184" s="15" t="s">
+    <row r="184" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A184" s="2" t="s">
         <v>136</v>
       </c>
       <c r="B184" s="16" t="s">
@@ -4948,8 +4962,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A185" s="15" t="s">
+    <row r="185" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A185" s="2" t="s">
         <v>137</v>
       </c>
       <c r="B185" s="16" t="s">
@@ -4965,8 +4979,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A186" s="15" t="s">
+    <row r="186" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A186" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B186" s="16" t="s">
@@ -4982,8 +4996,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A187" s="15" t="s">
+    <row r="187" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A187" s="2" t="s">
         <v>139</v>
       </c>
       <c r="B187" s="16" t="s">
@@ -4999,8 +5013,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A188" s="15" t="s">
+    <row r="188" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A188" s="2" t="s">
         <v>140</v>
       </c>
       <c r="B188" s="16" t="s">
@@ -5016,8 +5030,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A189" s="15" t="s">
+    <row r="189" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A189" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B189" s="16" t="s">
@@ -5033,8 +5047,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A190" s="15" t="s">
+    <row r="190" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A190" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B190" s="16" t="s">
@@ -5050,8 +5064,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A191" s="15" t="s">
+    <row r="191" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A191" s="2" t="s">
         <v>101</v>
       </c>
       <c r="B191" s="16" t="s">
@@ -5067,8 +5081,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A192" s="15" t="s">
+    <row r="192" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A192" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B192" s="16" t="s">
@@ -5084,8 +5098,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A193" s="15" t="s">
+    <row r="193" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A193" s="2" t="s">
         <v>103</v>
       </c>
       <c r="B193" s="16" t="s">
@@ -5101,8 +5115,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A194" s="15" t="s">
+    <row r="194" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A194" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B194" s="16" t="s">
@@ -5118,8 +5132,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A195" s="15" t="s">
+    <row r="195" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A195" s="2" t="s">
         <v>105</v>
       </c>
       <c r="B195" s="16" t="s">
@@ -5135,8 +5149,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A196" s="15" t="s">
+    <row r="196" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A196" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B196" s="16" t="s">
@@ -5152,8 +5166,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A197" s="15" t="s">
+    <row r="197" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A197" s="2" t="s">
         <v>107</v>
       </c>
       <c r="B197" s="16" t="s">
@@ -5169,8 +5183,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A198" s="15" t="s">
+    <row r="198" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A198" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B198" s="16" t="s">
@@ -5186,8 +5200,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A199" s="15" t="s">
+    <row r="199" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A199" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B199" s="16" t="s">
@@ -5203,8 +5217,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A200" s="15" t="s">
+    <row r="200" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A200" s="2" t="s">
         <v>111</v>
       </c>
       <c r="B200" s="16" t="s">
@@ -5220,8 +5234,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A201" s="15" t="s">
+    <row r="201" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A201" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B201" s="16" t="s">
@@ -5237,8 +5251,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A202" s="15" t="s">
+    <row r="202" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A202" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B202" s="16" t="s">
@@ -5254,8 +5268,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A203" s="15" t="s">
+    <row r="203" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A203" s="2" t="s">
         <v>115</v>
       </c>
       <c r="B203" s="16" t="s">
@@ -5271,8 +5285,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A204" s="15" t="s">
+    <row r="204" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A204" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B204" s="16" t="s">
@@ -5288,8 +5302,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A205" s="15" t="s">
+    <row r="205" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A205" s="2" t="s">
         <v>118</v>
       </c>
       <c r="B205" s="16" t="s">
@@ -5305,8 +5319,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A206" s="15" t="s">
+    <row r="206" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A206" s="2" t="s">
         <v>119</v>
       </c>
       <c r="B206" s="16" t="s">
@@ -5322,8 +5336,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A207" s="15" t="s">
+    <row r="207" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A207" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B207" s="16" t="s">
@@ -5339,8 +5353,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A208" s="15" t="s">
+    <row r="208" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A208" s="2" t="s">
         <v>121</v>
       </c>
       <c r="B208" s="16" t="s">
@@ -5356,8 +5370,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A209" s="15" t="s">
+    <row r="209" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A209" s="2" t="s">
         <v>122</v>
       </c>
       <c r="B209" s="16" t="s">
@@ -5373,8 +5387,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A210" s="15" t="s">
+    <row r="210" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A210" s="2" t="s">
         <v>123</v>
       </c>
       <c r="B210" s="16" t="s">
@@ -5390,8 +5404,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A211" s="15" t="s">
+    <row r="211" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A211" s="2" t="s">
         <v>124</v>
       </c>
       <c r="B211" s="16" t="s">
@@ -5407,8 +5421,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A212" s="15" t="s">
+    <row r="212" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A212" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B212" s="16" t="s">
@@ -5424,8 +5438,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A213" s="15" t="s">
+    <row r="213" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A213" s="2" t="s">
         <v>127</v>
       </c>
       <c r="B213" s="16" t="s">
@@ -5441,8 +5455,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A214" s="15" t="s">
+    <row r="214" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A214" s="2" t="s">
         <v>128</v>
       </c>
       <c r="B214" s="16" t="s">
@@ -5458,8 +5472,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A215" s="15" t="s">
+    <row r="215" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A215" s="2" t="s">
         <v>129</v>
       </c>
       <c r="B215" s="16" t="s">
@@ -5475,8 +5489,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A216" s="15" t="s">
+    <row r="216" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A216" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B216" s="16" t="s">
@@ -5492,8 +5506,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A217" s="15" t="s">
+    <row r="217" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A217" s="2" t="s">
         <v>131</v>
       </c>
       <c r="B217" s="16" t="s">
@@ -5509,8 +5523,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A218" s="15" t="s">
+    <row r="218" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A218" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B218" s="16" t="s">
@@ -5526,8 +5540,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A219" s="15" t="s">
+    <row r="219" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A219" s="2" t="s">
         <v>133</v>
       </c>
       <c r="B219" s="16" t="s">
@@ -5543,8 +5557,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A220" s="15" t="s">
+    <row r="220" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A220" s="2" t="s">
         <v>135</v>
       </c>
       <c r="B220" s="16" t="s">
@@ -5560,8 +5574,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A221" s="15" t="s">
+    <row r="221" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A221" s="2" t="s">
         <v>136</v>
       </c>
       <c r="B221" s="16" t="s">
@@ -5577,8 +5591,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A222" s="15" t="s">
+    <row r="222" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A222" s="2" t="s">
         <v>137</v>
       </c>
       <c r="B222" s="16" t="s">
@@ -5594,8 +5608,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A223" s="15" t="s">
+    <row r="223" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A223" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B223" s="16" t="s">
@@ -5611,8 +5625,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A224" s="15" t="s">
+    <row r="224" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A224" s="2" t="s">
         <v>139</v>
       </c>
       <c r="B224" s="16" t="s">
@@ -5628,8 +5642,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A225" s="15" t="s">
+    <row r="225" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A225" s="2" t="s">
         <v>140</v>
       </c>
       <c r="B225" s="16" t="s">
@@ -5645,8 +5659,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A226" s="15" t="s">
+    <row r="226" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A226" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B226" s="16" t="s">
@@ -5662,8 +5676,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A227" s="15" t="s">
+    <row r="227" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A227" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B227" s="16" t="s">
@@ -5679,8 +5693,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A228" s="15" t="s">
+    <row r="228" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A228" s="2" t="s">
         <v>101</v>
       </c>
       <c r="B228" s="16" t="s">
@@ -5696,8 +5710,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A229" s="15" t="s">
+    <row r="229" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A229" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B229" s="16" t="s">
@@ -5713,8 +5727,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A230" s="15" t="s">
+    <row r="230" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A230" s="2" t="s">
         <v>103</v>
       </c>
       <c r="B230" s="16" t="s">
@@ -5730,8 +5744,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A231" s="15" t="s">
+    <row r="231" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A231" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B231" s="16" t="s">
@@ -5747,8 +5761,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A232" s="15" t="s">
+    <row r="232" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A232" s="2" t="s">
         <v>105</v>
       </c>
       <c r="B232" s="16" t="s">
@@ -5764,8 +5778,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A233" s="15" t="s">
+    <row r="233" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A233" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B233" s="16" t="s">
@@ -5781,8 +5795,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A234" s="15" t="s">
+    <row r="234" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A234" s="2" t="s">
         <v>107</v>
       </c>
       <c r="B234" s="16" t="s">
@@ -5798,8 +5812,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A235" s="15" t="s">
+    <row r="235" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A235" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B235" s="16" t="s">
@@ -5815,8 +5829,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A236" s="15" t="s">
+    <row r="236" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A236" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B236" s="16" t="s">
@@ -5832,8 +5846,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A237" s="15" t="s">
+    <row r="237" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A237" s="2" t="s">
         <v>111</v>
       </c>
       <c r="B237" s="16" t="s">
@@ -5849,8 +5863,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A238" s="15" t="s">
+    <row r="238" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A238" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B238" s="16" t="s">
@@ -5866,8 +5880,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A239" s="15" t="s">
+    <row r="239" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A239" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B239" s="16" t="s">
@@ -5883,8 +5897,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A240" s="15" t="s">
+    <row r="240" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A240" s="2" t="s">
         <v>115</v>
       </c>
       <c r="B240" s="16" t="s">
@@ -5900,8 +5914,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A241" s="15" t="s">
+    <row r="241" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A241" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B241" s="16" t="s">
@@ -5917,8 +5931,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A242" s="15" t="s">
+    <row r="242" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A242" s="2" t="s">
         <v>118</v>
       </c>
       <c r="B242" s="16" t="s">
@@ -5934,8 +5948,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A243" s="15" t="s">
+    <row r="243" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A243" s="2" t="s">
         <v>119</v>
       </c>
       <c r="B243" s="16" t="s">
@@ -5951,8 +5965,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A244" s="15" t="s">
+    <row r="244" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A244" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B244" s="16" t="s">
@@ -5968,8 +5982,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A245" s="15" t="s">
+    <row r="245" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A245" s="2" t="s">
         <v>121</v>
       </c>
       <c r="B245" s="16" t="s">
@@ -5985,8 +5999,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A246" s="15" t="s">
+    <row r="246" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A246" s="2" t="s">
         <v>122</v>
       </c>
       <c r="B246" s="16" t="s">
@@ -6002,8 +6016,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A247" s="15" t="s">
+    <row r="247" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A247" s="2" t="s">
         <v>123</v>
       </c>
       <c r="B247" s="16" t="s">
@@ -6019,8 +6033,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A248" s="15" t="s">
+    <row r="248" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A248" s="2" t="s">
         <v>124</v>
       </c>
       <c r="B248" s="16" t="s">
@@ -6036,8 +6050,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A249" s="15" t="s">
+    <row r="249" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A249" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B249" s="16" t="s">
@@ -6053,8 +6067,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A250" s="15" t="s">
+    <row r="250" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A250" s="2" t="s">
         <v>127</v>
       </c>
       <c r="B250" s="16" t="s">
@@ -6070,8 +6084,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A251" s="15" t="s">
+    <row r="251" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A251" s="2" t="s">
         <v>128</v>
       </c>
       <c r="B251" s="16" t="s">
@@ -6087,8 +6101,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A252" s="15" t="s">
+    <row r="252" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A252" s="2" t="s">
         <v>129</v>
       </c>
       <c r="B252" s="16" t="s">
@@ -6104,8 +6118,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A253" s="15" t="s">
+    <row r="253" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A253" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B253" s="16" t="s">
@@ -6121,8 +6135,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A254" s="15" t="s">
+    <row r="254" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A254" s="2" t="s">
         <v>131</v>
       </c>
       <c r="B254" s="16" t="s">
@@ -6138,8 +6152,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A255" s="15" t="s">
+    <row r="255" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A255" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B255" s="16" t="s">
@@ -6155,8 +6169,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A256" s="15" t="s">
+    <row r="256" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A256" s="2" t="s">
         <v>133</v>
       </c>
       <c r="B256" s="16" t="s">
@@ -6172,8 +6186,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A257" s="15" t="s">
+    <row r="257" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A257" s="2" t="s">
         <v>135</v>
       </c>
       <c r="B257" s="16" t="s">
@@ -6189,8 +6203,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A258" s="15" t="s">
+    <row r="258" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A258" s="2" t="s">
         <v>136</v>
       </c>
       <c r="B258" s="16" t="s">
@@ -6206,8 +6220,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A259" s="15" t="s">
+    <row r="259" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A259" s="2" t="s">
         <v>137</v>
       </c>
       <c r="B259" s="16" t="s">
@@ -6223,8 +6237,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A260" s="15" t="s">
+    <row r="260" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A260" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B260" s="16" t="s">
@@ -6240,8 +6254,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A261" s="15" t="s">
+    <row r="261" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A261" s="2" t="s">
         <v>139</v>
       </c>
       <c r="B261" s="16" t="s">
@@ -6257,8 +6271,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A262" s="15" t="s">
+    <row r="262" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A262" s="2" t="s">
         <v>140</v>
       </c>
       <c r="B262" s="16" t="s">
@@ -6274,8 +6288,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A263" s="15" t="s">
+    <row r="263" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A263" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B263" s="16" t="s">
@@ -6291,8 +6305,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A264" s="15" t="s">
+    <row r="264" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A264" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B264" s="16" t="s">
@@ -6308,8 +6322,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A265" s="15" t="s">
+    <row r="265" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A265" s="2" t="s">
         <v>101</v>
       </c>
       <c r="B265" s="16" t="s">
@@ -6325,8 +6339,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A266" s="15" t="s">
+    <row r="266" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A266" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B266" s="16" t="s">
@@ -6342,8 +6356,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A267" s="15" t="s">
+    <row r="267" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A267" s="2" t="s">
         <v>103</v>
       </c>
       <c r="B267" s="16" t="s">
@@ -6359,8 +6373,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A268" s="15" t="s">
+    <row r="268" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A268" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B268" s="16" t="s">
@@ -6376,8 +6390,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A269" s="15" t="s">
+    <row r="269" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A269" s="2" t="s">
         <v>105</v>
       </c>
       <c r="B269" s="16" t="s">
@@ -6393,8 +6407,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A270" s="15" t="s">
+    <row r="270" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A270" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B270" s="16" t="s">
@@ -6410,8 +6424,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A271" s="15" t="s">
+    <row r="271" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A271" s="2" t="s">
         <v>107</v>
       </c>
       <c r="B271" s="16" t="s">
@@ -6427,8 +6441,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A272" s="15" t="s">
+    <row r="272" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A272" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B272" s="16" t="s">
@@ -6444,8 +6458,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A273" s="15" t="s">
+    <row r="273" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A273" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B273" s="16" t="s">
@@ -6461,8 +6475,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A274" s="15" t="s">
+    <row r="274" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A274" s="2" t="s">
         <v>111</v>
       </c>
       <c r="B274" s="16" t="s">
@@ -6478,8 +6492,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A275" s="15" t="s">
+    <row r="275" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A275" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B275" s="16" t="s">
@@ -6495,8 +6509,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A276" s="15" t="s">
+    <row r="276" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A276" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B276" s="16" t="s">
@@ -6512,8 +6526,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A277" s="15" t="s">
+    <row r="277" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A277" s="2" t="s">
         <v>115</v>
       </c>
       <c r="B277" s="16" t="s">
@@ -6529,8 +6543,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A278" s="15" t="s">
+    <row r="278" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A278" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B278" s="16" t="s">
@@ -6546,8 +6560,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A279" s="15" t="s">
+    <row r="279" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A279" s="2" t="s">
         <v>118</v>
       </c>
       <c r="B279" s="16" t="s">
@@ -6563,8 +6577,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A280" s="15" t="s">
+    <row r="280" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A280" s="2" t="s">
         <v>119</v>
       </c>
       <c r="B280" s="16" t="s">
@@ -6580,8 +6594,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A281" s="15" t="s">
+    <row r="281" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A281" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B281" s="16" t="s">
@@ -6597,8 +6611,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A282" s="15" t="s">
+    <row r="282" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A282" s="2" t="s">
         <v>121</v>
       </c>
       <c r="B282" s="16" t="s">
@@ -6614,8 +6628,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A283" s="15" t="s">
+    <row r="283" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A283" s="2" t="s">
         <v>122</v>
       </c>
       <c r="B283" s="16" t="s">
@@ -6631,8 +6645,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A284" s="15" t="s">
+    <row r="284" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A284" s="2" t="s">
         <v>123</v>
       </c>
       <c r="B284" s="16" t="s">
@@ -6648,8 +6662,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A285" s="15" t="s">
+    <row r="285" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A285" s="2" t="s">
         <v>124</v>
       </c>
       <c r="B285" s="16" t="s">
@@ -6665,8 +6679,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A286" s="15" t="s">
+    <row r="286" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A286" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B286" s="16" t="s">
@@ -6682,8 +6696,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A287" s="15" t="s">
+    <row r="287" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A287" s="2" t="s">
         <v>127</v>
       </c>
       <c r="B287" s="16" t="s">
@@ -6699,8 +6713,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A288" s="15" t="s">
+    <row r="288" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A288" s="2" t="s">
         <v>128</v>
       </c>
       <c r="B288" s="16" t="s">
@@ -6716,8 +6730,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A289" s="15" t="s">
+    <row r="289" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A289" s="2" t="s">
         <v>129</v>
       </c>
       <c r="B289" s="16" t="s">
@@ -6733,8 +6747,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A290" s="15" t="s">
+    <row r="290" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A290" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B290" s="16" t="s">
@@ -6750,8 +6764,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A291" s="15" t="s">
+    <row r="291" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A291" s="2" t="s">
         <v>131</v>
       </c>
       <c r="B291" s="16" t="s">
@@ -6767,8 +6781,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A292" s="15" t="s">
+    <row r="292" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A292" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B292" s="16" t="s">
@@ -6784,8 +6798,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A293" s="15" t="s">
+    <row r="293" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A293" s="2" t="s">
         <v>133</v>
       </c>
       <c r="B293" s="16" t="s">
@@ -6801,8 +6815,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A294" s="15" t="s">
+    <row r="294" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A294" s="2" t="s">
         <v>135</v>
       </c>
       <c r="B294" s="16" t="s">
@@ -6818,8 +6832,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A295" s="15" t="s">
+    <row r="295" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A295" s="2" t="s">
         <v>136</v>
       </c>
       <c r="B295" s="16" t="s">
@@ -6835,8 +6849,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A296" s="15" t="s">
+    <row r="296" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A296" s="2" t="s">
         <v>137</v>
       </c>
       <c r="B296" s="16" t="s">
@@ -6852,8 +6866,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A297" s="15" t="s">
+    <row r="297" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A297" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B297" s="16" t="s">
@@ -6869,8 +6883,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A298" s="15" t="s">
+    <row r="298" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A298" s="2" t="s">
         <v>139</v>
       </c>
       <c r="B298" s="16" t="s">
@@ -6886,8 +6900,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A299" s="15" t="s">
+    <row r="299" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A299" s="2" t="s">
         <v>140</v>
       </c>
       <c r="B299" s="16" t="s">
@@ -6903,8 +6917,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A300" s="15" t="s">
+    <row r="300" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A300" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B300" s="16" t="s">
@@ -6920,8 +6934,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A301" s="15" t="s">
+    <row r="301" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A301" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B301" s="16" t="s">
@@ -6937,8 +6951,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A302" s="15" t="s">
+    <row r="302" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A302" s="2" t="s">
         <v>101</v>
       </c>
       <c r="B302" s="16" t="s">
@@ -6954,8 +6968,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A303" s="15" t="s">
+    <row r="303" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A303" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B303" s="16" t="s">
@@ -6971,8 +6985,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A304" s="15" t="s">
+    <row r="304" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A304" s="2" t="s">
         <v>103</v>
       </c>
       <c r="B304" s="16" t="s">
@@ -6988,8 +7002,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A305" s="15" t="s">
+    <row r="305" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A305" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B305" s="16" t="s">
@@ -7005,8 +7019,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A306" s="15" t="s">
+    <row r="306" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A306" s="2" t="s">
         <v>105</v>
       </c>
       <c r="B306" s="16" t="s">
@@ -7022,8 +7036,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A307" s="15" t="s">
+    <row r="307" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A307" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B307" s="16" t="s">
@@ -7039,8 +7053,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A308" s="15" t="s">
+    <row r="308" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A308" s="2" t="s">
         <v>107</v>
       </c>
       <c r="B308" s="16" t="s">
@@ -7056,8 +7070,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A309" s="15" t="s">
+    <row r="309" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A309" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B309" s="16" t="s">
@@ -7073,8 +7087,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A310" s="15" t="s">
+    <row r="310" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A310" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B310" s="16" t="s">
@@ -7090,8 +7104,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A311" s="15" t="s">
+    <row r="311" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A311" s="2" t="s">
         <v>111</v>
       </c>
       <c r="B311" s="16" t="s">
@@ -7107,8 +7121,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A312" s="15" t="s">
+    <row r="312" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A312" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B312" s="16" t="s">
@@ -7124,8 +7138,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A313" s="15" t="s">
+    <row r="313" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A313" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B313" s="16" t="s">
@@ -7141,8 +7155,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A314" s="15" t="s">
+    <row r="314" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A314" s="2" t="s">
         <v>115</v>
       </c>
       <c r="B314" s="16" t="s">
@@ -7158,8 +7172,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A315" s="15" t="s">
+    <row r="315" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A315" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B315" s="16" t="s">
@@ -7175,8 +7189,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A316" s="15" t="s">
+    <row r="316" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A316" s="2" t="s">
         <v>118</v>
       </c>
       <c r="B316" s="16" t="s">
@@ -7192,8 +7206,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A317" s="15" t="s">
+    <row r="317" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A317" s="2" t="s">
         <v>119</v>
       </c>
       <c r="B317" s="16" t="s">
@@ -7209,8 +7223,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A318" s="15" t="s">
+    <row r="318" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A318" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B318" s="16" t="s">
@@ -7226,8 +7240,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A319" s="15" t="s">
+    <row r="319" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A319" s="2" t="s">
         <v>121</v>
       </c>
       <c r="B319" s="16" t="s">
@@ -7243,8 +7257,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A320" s="15" t="s">
+    <row r="320" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A320" s="2" t="s">
         <v>122</v>
       </c>
       <c r="B320" s="16" t="s">
@@ -7260,8 +7274,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A321" s="15" t="s">
+    <row r="321" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A321" s="2" t="s">
         <v>123</v>
       </c>
       <c r="B321" s="16" t="s">
@@ -7277,8 +7291,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A322" s="15" t="s">
+    <row r="322" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A322" s="2" t="s">
         <v>124</v>
       </c>
       <c r="B322" s="16" t="s">
@@ -7294,8 +7308,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A323" s="15" t="s">
+    <row r="323" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A323" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B323" s="16" t="s">
@@ -7311,8 +7325,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A324" s="15" t="s">
+    <row r="324" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A324" s="2" t="s">
         <v>127</v>
       </c>
       <c r="B324" s="16" t="s">
@@ -7328,8 +7342,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A325" s="15" t="s">
+    <row r="325" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A325" s="2" t="s">
         <v>128</v>
       </c>
       <c r="B325" s="16" t="s">
@@ -7345,8 +7359,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A326" s="15" t="s">
+    <row r="326" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A326" s="2" t="s">
         <v>129</v>
       </c>
       <c r="B326" s="16" t="s">
@@ -7362,8 +7376,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A327" s="15" t="s">
+    <row r="327" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A327" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B327" s="16" t="s">
@@ -7379,8 +7393,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A328" s="15" t="s">
+    <row r="328" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A328" s="2" t="s">
         <v>131</v>
       </c>
       <c r="B328" s="16" t="s">
@@ -7396,8 +7410,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A329" s="15" t="s">
+    <row r="329" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A329" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B329" s="16" t="s">
@@ -7413,8 +7427,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A330" s="15" t="s">
+    <row r="330" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A330" s="2" t="s">
         <v>133</v>
       </c>
       <c r="B330" s="16" t="s">
@@ -7430,8 +7444,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A331" s="15" t="s">
+    <row r="331" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A331" s="2" t="s">
         <v>135</v>
       </c>
       <c r="B331" s="16" t="s">
@@ -7447,8 +7461,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A332" s="15" t="s">
+    <row r="332" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A332" s="2" t="s">
         <v>136</v>
       </c>
       <c r="B332" s="16" t="s">
@@ -7464,8 +7478,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A333" s="15" t="s">
+    <row r="333" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A333" s="2" t="s">
         <v>137</v>
       </c>
       <c r="B333" s="16" t="s">
@@ -7481,8 +7495,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A334" s="15" t="s">
+    <row r="334" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A334" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B334" s="16" t="s">
@@ -7498,8 +7512,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A335" s="15" t="s">
+    <row r="335" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A335" s="2" t="s">
         <v>139</v>
       </c>
       <c r="B335" s="16" t="s">
@@ -7515,8 +7529,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A336" s="15" t="s">
+    <row r="336" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A336" s="2" t="s">
         <v>140</v>
       </c>
       <c r="B336" s="16" t="s">
@@ -7532,8 +7546,8 @@
         <v>40</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A337" s="15" t="s">
+    <row r="337" spans="1:5" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A337" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B337" s="16" t="s">
@@ -7567,982 +7581,982 @@
     <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:6" ht="23.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="35" t="s">
         <v>182</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-    </row>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+    </row>
+    <row r="3" spans="1:6" ht="50.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+    <row r="4" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A4" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A4)</f>
         <v>9</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A4,Data!$C$5:$C$337,"Y")</f>
         <v>9</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A4,Data!$C$5:$C$337,"Y")/60</f>
         <v>4.5</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A4,Data!$C$5:$C$337,"Y")</f>
         <v>360</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="8">
         <f t="shared" ref="F4:F41" si="0">IFERROR(E4/D4,0)</f>
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A5" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A5)</f>
         <v>9</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A5,Data!$C$5:$C$337,"Y")</f>
         <v>9</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A5,Data!$C$5:$C$337,"Y")/60</f>
         <v>4.5</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A5,Data!$C$5:$C$337,"Y")</f>
         <v>360</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
+    <row r="6" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A6" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A6)</f>
         <v>9</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A6,Data!$C$5:$C$337,"Y")</f>
         <v>9</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A6,Data!$C$5:$C$337,"Y")/60</f>
         <v>4.5</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A6,Data!$C$5:$C$337,"Y")</f>
         <v>360</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
+    <row r="7" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A7" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A7)</f>
         <v>9</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A7,Data!$C$5:$C$337,"Y")</f>
         <v>8</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A7,Data!$C$5:$C$337,"Y")/60</f>
         <v>4</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A7,Data!$C$5:$C$337,"Y")</f>
         <v>320</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+    <row r="8" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A8" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A8)</f>
         <v>9</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A8,Data!$C$5:$C$337,"Y")</f>
         <v>8</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A8,Data!$C$5:$C$337,"Y")/60</f>
         <v>4</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A8,Data!$C$5:$C$337,"Y")</f>
         <v>320</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="s">
+    <row r="9" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A9" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A9)</f>
         <v>9</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A9,Data!$C$5:$C$337,"Y")</f>
         <v>8</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A9,Data!$C$5:$C$337,"Y")/60</f>
         <v>4</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A9,Data!$C$5:$C$337,"Y")</f>
         <v>320</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="s">
+    <row r="10" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A10" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A10)</f>
         <v>9</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A10,Data!$C$5:$C$337,"Y")</f>
         <v>7</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A10,Data!$C$5:$C$337,"Y")/60</f>
         <v>3.5</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A10,Data!$C$5:$C$337,"Y")</f>
         <v>280</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="20" t="s">
+    <row r="11" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A11" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A11)</f>
         <v>9</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A11,Data!$C$5:$C$337,"Y")</f>
         <v>8</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A11,Data!$C$5:$C$337,"Y")/60</f>
         <v>4</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A11,Data!$C$5:$C$337,"Y")</f>
         <v>320</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="20" t="s">
+    <row r="12" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A12" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A12)</f>
         <v>9</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A12,Data!$C$5:$C$337,"Y")</f>
         <v>8</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A12,Data!$C$5:$C$337,"Y")/60</f>
         <v>4</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A12,Data!$C$5:$C$337,"Y")</f>
         <v>320</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="20" t="s">
+    <row r="13" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A13" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A13)</f>
         <v>9</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A13,Data!$C$5:$C$337,"Y")</f>
         <v>9</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A13,Data!$C$5:$C$337,"Y")/60</f>
         <v>4.5</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A13,Data!$C$5:$C$337,"Y")</f>
         <v>360</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="20" t="s">
+    <row r="14" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A14" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A14)</f>
         <v>9</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A14,Data!$C$5:$C$337,"Y")</f>
         <v>9</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A14,Data!$C$5:$C$337,"Y")/60</f>
         <v>4.5</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A14,Data!$C$5:$C$337,"Y")</f>
         <v>360</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="20" t="s">
+    <row r="15" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A15" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A15)</f>
         <v>9</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A15,Data!$C$5:$C$337,"Y")</f>
         <v>7</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A15,Data!$C$5:$C$337,"Y")/60</f>
         <v>3.5</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A15,Data!$C$5:$C$337,"Y")</f>
         <v>280</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="20" t="s">
+    <row r="16" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A16" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A16)</f>
         <v>9</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A16,Data!$C$5:$C$337,"Y")</f>
         <v>9</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A16,Data!$C$5:$C$337,"Y")/60</f>
         <v>4.5</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A16,Data!$C$5:$C$337,"Y")</f>
         <v>360</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="20" t="s">
+    <row r="17" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A17" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A17)</f>
         <v>9</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A17,Data!$C$5:$C$337,"Y")</f>
         <v>8</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A17,Data!$C$5:$C$337,"Y")/60</f>
         <v>4</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A17,Data!$C$5:$C$337,"Y")</f>
         <v>320</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="20" t="s">
+    <row r="18" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A18" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A18)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A18,Data!$C$5:$C$337,"Y")</f>
         <v>8</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A18,Data!$C$5:$C$337,"Y")/60</f>
         <v>4</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A18,Data!$C$5:$C$337,"Y")</f>
         <v>320</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="20" t="s">
+    <row r="19" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A19" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A19)</f>
         <v>9</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A19,Data!$C$5:$C$337,"Y")</f>
         <v>8</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A19,Data!$C$5:$C$337,"Y")/60</f>
         <v>4</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A19,Data!$C$5:$C$337,"Y")</f>
         <v>320</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="20" t="s">
+    <row r="20" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A20" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A20)</f>
         <v>9</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A20,Data!$C$5:$C$337,"Y")</f>
         <v>8</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A20,Data!$C$5:$C$337,"Y")/60</f>
         <v>4</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A20,Data!$C$5:$C$337,"Y")</f>
         <v>320</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="20" t="s">
+    <row r="21" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A21" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A21)</f>
         <v>9</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A21,Data!$C$5:$C$337,"Y")</f>
         <v>7</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A21,Data!$C$5:$C$337,"Y")/60</f>
         <v>3.5</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A21,Data!$C$5:$C$337,"Y")</f>
         <v>280</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="20" t="s">
+    <row r="22" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A22" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A22)</f>
         <v>9</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A22,Data!$C$5:$C$337,"Y")</f>
         <v>8</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A22,Data!$C$5:$C$337,"Y")/60</f>
         <v>4</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A22,Data!$C$5:$C$337,"Y")</f>
         <v>320</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="20" t="s">
+    <row r="23" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A23" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A23)</f>
         <v>9</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A23,Data!$C$5:$C$337,"Y")</f>
         <v>5</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A23,Data!$C$5:$C$337,"Y")/60</f>
         <v>2.5</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A23,Data!$C$5:$C$337,"Y")</f>
         <v>200</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="20" t="s">
+    <row r="24" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A24" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A24)</f>
         <v>9</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A24,Data!$C$5:$C$337,"Y")</f>
         <v>8</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A24,Data!$C$5:$C$337,"Y")/60</f>
         <v>4</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A24,Data!$C$5:$C$337,"Y")</f>
         <v>320</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="20" t="s">
+    <row r="25" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A25" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A25)</f>
         <v>10</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C25" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A25,Data!$C$5:$C$337,"Y")</f>
         <v>9</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A25,Data!$C$5:$C$337,"Y")/60</f>
         <v>4.5</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A25,Data!$C$5:$C$337,"Y")</f>
         <v>360</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="20" t="s">
+    <row r="26" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A26" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A26)</f>
         <v>10</v>
       </c>
-      <c r="C26" s="10">
+      <c r="C26" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A26,Data!$C$5:$C$337,"Y")</f>
         <v>9</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A26,Data!$C$5:$C$337,"Y")/60</f>
         <v>4.5</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A26,Data!$C$5:$C$337,"Y")</f>
         <v>360</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="20" t="s">
+    <row r="27" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A27" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A27)</f>
         <v>10</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A27,Data!$C$5:$C$337,"Y")</f>
         <v>9</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A27,Data!$C$5:$C$337,"Y")/60</f>
         <v>4.5</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A27,Data!$C$5:$C$337,"Y")</f>
         <v>360</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="20" t="s">
+    <row r="28" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A28" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A28)</f>
         <v>10</v>
       </c>
-      <c r="C28" s="10">
+      <c r="C28" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A28,Data!$C$5:$C$337,"Y")</f>
         <v>10</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A28,Data!$C$5:$C$337,"Y")/60</f>
         <v>5</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A28,Data!$C$5:$C$337,"Y")</f>
         <v>400</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="20" t="s">
+    <row r="29" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A29" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A29)</f>
         <v>10</v>
       </c>
-      <c r="C29" s="10">
+      <c r="C29" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A29,Data!$C$5:$C$337,"Y")</f>
         <v>8</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D29" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A29,Data!$C$5:$C$337,"Y")/60</f>
         <v>4</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A29,Data!$C$5:$C$337,"Y")</f>
         <v>320</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F29" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="20" t="s">
+    <row r="30" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A30" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A30)</f>
         <v>10</v>
       </c>
-      <c r="C30" s="10">
+      <c r="C30" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A30,Data!$C$5:$C$337,"Y")</f>
         <v>10</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A30,Data!$C$5:$C$337,"Y")/60</f>
         <v>5</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A30,Data!$C$5:$C$337,"Y")</f>
         <v>400</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="20" t="s">
+    <row r="31" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A31" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A31)</f>
         <v>10</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A31,Data!$C$5:$C$337,"Y")</f>
         <v>9</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A31,Data!$C$5:$C$337,"Y")/60</f>
         <v>4.5</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A31,Data!$C$5:$C$337,"Y")</f>
         <v>360</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="20" t="s">
+    <row r="32" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A32" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A32)</f>
         <v>10</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C32" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A32,Data!$C$5:$C$337,"Y")</f>
         <v>10</v>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A32,Data!$C$5:$C$337,"Y")/60</f>
         <v>5</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E32" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A32,Data!$C$5:$C$337,"Y")</f>
         <v>400</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="20" t="s">
+    <row r="33" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A33" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A33)</f>
         <v>8</v>
       </c>
-      <c r="C33" s="10">
+      <c r="C33" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A33,Data!$C$5:$C$337,"Y")</f>
         <v>8</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D33" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A33,Data!$C$5:$C$337,"Y")/60</f>
         <v>4</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A33,Data!$C$5:$C$337,"Y")</f>
         <v>320</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F33" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="20" t="s">
+    <row r="34" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A34" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A34)</f>
         <v>8</v>
       </c>
-      <c r="C34" s="10">
+      <c r="C34" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A34,Data!$C$5:$C$337,"Y")</f>
         <v>8</v>
       </c>
-      <c r="D34" s="14">
+      <c r="D34" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A34,Data!$C$5:$C$337,"Y")/60</f>
         <v>4</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A34,Data!$C$5:$C$337,"Y")</f>
         <v>320</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F34" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="20" t="s">
+    <row r="35" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A35" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A35)</f>
         <v>8</v>
       </c>
-      <c r="C35" s="10">
+      <c r="C35" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A35,Data!$C$5:$C$337,"Y")</f>
         <v>8</v>
       </c>
-      <c r="D35" s="14">
+      <c r="D35" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A35,Data!$C$5:$C$337,"Y")/60</f>
         <v>4</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A35,Data!$C$5:$C$337,"Y")</f>
         <v>320</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="20" t="s">
+    <row r="36" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A36" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A36)</f>
         <v>8</v>
       </c>
-      <c r="C36" s="10">
+      <c r="C36" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A36,Data!$C$5:$C$337,"Y")</f>
         <v>6</v>
       </c>
-      <c r="D36" s="14">
+      <c r="D36" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A36,Data!$C$5:$C$337,"Y")/60</f>
         <v>3</v>
       </c>
-      <c r="E36" s="7">
+      <c r="E36" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A36,Data!$C$5:$C$337,"Y")</f>
         <v>240</v>
       </c>
-      <c r="F36" s="7">
+      <c r="F36" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="20" t="s">
+    <row r="37" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A37" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A37)</f>
         <v>8</v>
       </c>
-      <c r="C37" s="10">
+      <c r="C37" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A37,Data!$C$5:$C$337,"Y")</f>
         <v>6</v>
       </c>
-      <c r="D37" s="14">
+      <c r="D37" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A37,Data!$C$5:$C$337,"Y")/60</f>
         <v>3</v>
       </c>
-      <c r="E37" s="7">
+      <c r="E37" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A37,Data!$C$5:$C$337,"Y")</f>
         <v>240</v>
       </c>
-      <c r="F37" s="7">
+      <c r="F37" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="20" t="s">
+    <row r="38" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A38" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A38)</f>
         <v>8</v>
       </c>
-      <c r="C38" s="10">
+      <c r="C38" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A38,Data!$C$5:$C$337,"Y")</f>
         <v>6</v>
       </c>
-      <c r="D38" s="14">
+      <c r="D38" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A38,Data!$C$5:$C$337,"Y")/60</f>
         <v>3</v>
       </c>
-      <c r="E38" s="7">
+      <c r="E38" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A38,Data!$C$5:$C$337,"Y")</f>
         <v>240</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F38" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="20" t="s">
+    <row r="39" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A39" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A39)</f>
         <v>8</v>
       </c>
-      <c r="C39" s="10">
+      <c r="C39" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A39,Data!$C$5:$C$337,"Y")</f>
         <v>6</v>
       </c>
-      <c r="D39" s="14">
+      <c r="D39" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A39,Data!$C$5:$C$337,"Y")/60</f>
         <v>3</v>
       </c>
-      <c r="E39" s="7">
+      <c r="E39" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A39,Data!$C$5:$C$337,"Y")</f>
         <v>240</v>
       </c>
-      <c r="F39" s="7">
+      <c r="F39" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="20" t="s">
+    <row r="40" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A40" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B40" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A40)</f>
         <v>8</v>
       </c>
-      <c r="C40" s="10">
+      <c r="C40" s="11">
         <f>COUNTIFS(Data!$A$5:$A$337,A40,Data!$C$5:$C$337,"Y")</f>
         <v>6</v>
       </c>
-      <c r="D40" s="14">
+      <c r="D40" s="15">
         <f>SUMIFS(Data!$D$5:$D$337,Data!$A$5:$A$337,A40,Data!$C$5:$C$337,"Y")/60</f>
         <v>3</v>
       </c>
-      <c r="E40" s="7">
+      <c r="E40" s="8">
         <f>SUMIFS(Data!$E$5:$E$337,Data!$A$5:$A$337,A40,Data!$C$5:$C$337,"Y")</f>
         <v>240</v>
       </c>
-      <c r="F40" s="7">
+      <c r="F40" s="8">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="21" t="s">
+    <row r="41" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A41" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="B41" s="22">
+      <c r="B41" s="21">
         <f>SUM(B4:B40)</f>
         <v>333</v>
       </c>
-      <c r="C41" s="22">
+      <c r="C41" s="21">
         <f>SUM(C4:C40)</f>
         <v>296</v>
       </c>
-      <c r="D41" s="23">
+      <c r="D41" s="22">
         <f>SUM(D4:D40)</f>
         <v>148</v>
       </c>
-      <c r="E41" s="24">
+      <c r="E41" s="23">
         <f>SUM(E4:E40)</f>
         <v>11840</v>
       </c>
-      <c r="F41" s="24">
+      <c r="F41" s="23">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
@@ -8566,1357 +8580,1357 @@
     <col min="6" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:8" ht="23.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="35" t="s">
         <v>189</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-    </row>
-    <row r="4" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+    </row>
+    <row r="4" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="8">
         <f>Assumptions!$B$32*Assumptions!$B$17</f>
         <v>882</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+    <row r="5" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="15">
         <f>Assumptions!$B$25*Assumptions!$B$17</f>
         <v>67.5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:8" ht="50.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="6" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="str">
+    <row r="8" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A8" s="7" t="str">
         <f>'Revenue by student'!A4</f>
         <v>Student 01</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="11">
         <f>'Revenue by student'!C4</f>
         <v>9</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="12">
         <f>IFERROR(B8/'Revenue by student'!$C$41,0)</f>
         <v>3.0405405405405407E-2</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="8">
         <f t="shared" ref="D8:D44" si="0">C8*$B$4</f>
         <v>26.817567567567568</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="15">
         <f t="shared" ref="E8:E44" si="1">C8*$B$5</f>
         <v>2.0523648648648649</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <f>'Revenue by student'!E4</f>
         <v>360</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="8">
         <f t="shared" ref="G8:G44" si="2">F8-D8</f>
         <v>333.18243243243245</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="15">
         <f>'Revenue by student'!D4+E8</f>
         <v>6.5523648648648649</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="str">
+    <row r="9" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A9" s="7" t="str">
         <f>'Revenue by student'!A5</f>
         <v>Student 02</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="11">
         <f>'Revenue by student'!C5</f>
         <v>9</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="12">
         <f>IFERROR(B9/'Revenue by student'!$C$41,0)</f>
         <v>3.0405405405405407E-2</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="8">
         <f t="shared" si="0"/>
         <v>26.817567567567568</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="15">
         <f t="shared" si="1"/>
         <v>2.0523648648648649</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="8">
         <f>'Revenue by student'!E5</f>
         <v>360</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="8">
         <f t="shared" si="2"/>
         <v>333.18243243243245</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="15">
         <f>'Revenue by student'!D5+E9</f>
         <v>6.5523648648648649</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="str">
+    <row r="10" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A10" s="7" t="str">
         <f>'Revenue by student'!A6</f>
         <v>Student 03</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="11">
         <f>'Revenue by student'!C6</f>
         <v>9</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="12">
         <f>IFERROR(B10/'Revenue by student'!$C$41,0)</f>
         <v>3.0405405405405407E-2</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="8">
         <f t="shared" si="0"/>
         <v>26.817567567567568</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="15">
         <f t="shared" si="1"/>
         <v>2.0523648648648649</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="8">
         <f>'Revenue by student'!E6</f>
         <v>360</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="8">
         <f t="shared" si="2"/>
         <v>333.18243243243245</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="15">
         <f>'Revenue by student'!D6+E10</f>
         <v>6.5523648648648649</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="20" t="str">
+    <row r="11" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A11" s="7" t="str">
         <f>'Revenue by student'!A7</f>
         <v>Student 04</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="11">
         <f>'Revenue by student'!C7</f>
         <v>8</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="12">
         <f>IFERROR(B11/'Revenue by student'!$C$41,0)</f>
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="8">
         <f t="shared" si="0"/>
         <v>23.837837837837839</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="15">
         <f t="shared" si="1"/>
         <v>1.8243243243243243</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="8">
         <f>'Revenue by student'!E7</f>
         <v>320</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="8">
         <f t="shared" si="2"/>
         <v>296.16216216216219</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="15">
         <f>'Revenue by student'!D7+E11</f>
         <v>5.8243243243243246</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="20" t="str">
+    <row r="12" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A12" s="7" t="str">
         <f>'Revenue by student'!A8</f>
         <v>Student 05</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="11">
         <f>'Revenue by student'!C8</f>
         <v>8</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="12">
         <f>IFERROR(B12/'Revenue by student'!$C$41,0)</f>
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="8">
         <f t="shared" si="0"/>
         <v>23.837837837837839</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="15">
         <f t="shared" si="1"/>
         <v>1.8243243243243243</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="8">
         <f>'Revenue by student'!E8</f>
         <v>320</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="8">
         <f t="shared" si="2"/>
         <v>296.16216216216219</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="15">
         <f>'Revenue by student'!D8+E12</f>
         <v>5.8243243243243246</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="20" t="str">
+    <row r="13" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A13" s="7" t="str">
         <f>'Revenue by student'!A9</f>
         <v>Student 06</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="11">
         <f>'Revenue by student'!C9</f>
         <v>8</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="12">
         <f>IFERROR(B13/'Revenue by student'!$C$41,0)</f>
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="8">
         <f t="shared" si="0"/>
         <v>23.837837837837839</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="15">
         <f t="shared" si="1"/>
         <v>1.8243243243243243</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="8">
         <f>'Revenue by student'!E9</f>
         <v>320</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="8">
         <f t="shared" si="2"/>
         <v>296.16216216216219</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="15">
         <f>'Revenue by student'!D9+E13</f>
         <v>5.8243243243243246</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="20" t="str">
+    <row r="14" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A14" s="7" t="str">
         <f>'Revenue by student'!A10</f>
         <v>Student 07</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="11">
         <f>'Revenue by student'!C10</f>
         <v>7</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="12">
         <f>IFERROR(B14/'Revenue by student'!$C$41,0)</f>
         <v>2.364864864864865E-2</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="8">
         <f t="shared" si="0"/>
         <v>20.858108108108109</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="15">
         <f t="shared" si="1"/>
         <v>1.5962837837837838</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="8">
         <f>'Revenue by student'!E10</f>
         <v>280</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="8">
         <f t="shared" si="2"/>
         <v>259.14189189189187</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="15">
         <f>'Revenue by student'!D10+E14</f>
         <v>5.0962837837837842</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="20" t="str">
+    <row r="15" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A15" s="7" t="str">
         <f>'Revenue by student'!A11</f>
         <v>Student 08</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="11">
         <f>'Revenue by student'!C11</f>
         <v>8</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="12">
         <f>IFERROR(B15/'Revenue by student'!$C$41,0)</f>
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="8">
         <f t="shared" si="0"/>
         <v>23.837837837837839</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="15">
         <f t="shared" si="1"/>
         <v>1.8243243243243243</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="8">
         <f>'Revenue by student'!E11</f>
         <v>320</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="8">
         <f t="shared" si="2"/>
         <v>296.16216216216219</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="15">
         <f>'Revenue by student'!D11+E15</f>
         <v>5.8243243243243246</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="20" t="str">
+    <row r="16" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A16" s="7" t="str">
         <f>'Revenue by student'!A12</f>
         <v>Student 09</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="11">
         <f>'Revenue by student'!C12</f>
         <v>8</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="12">
         <f>IFERROR(B16/'Revenue by student'!$C$41,0)</f>
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="8">
         <f t="shared" si="0"/>
         <v>23.837837837837839</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="15">
         <f t="shared" si="1"/>
         <v>1.8243243243243243</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="8">
         <f>'Revenue by student'!E12</f>
         <v>320</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="8">
         <f t="shared" si="2"/>
         <v>296.16216216216219</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="15">
         <f>'Revenue by student'!D12+E16</f>
         <v>5.8243243243243246</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="20" t="str">
+    <row r="17" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A17" s="7" t="str">
         <f>'Revenue by student'!A13</f>
         <v>Student 10</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="11">
         <f>'Revenue by student'!C13</f>
         <v>9</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="12">
         <f>IFERROR(B17/'Revenue by student'!$C$41,0)</f>
         <v>3.0405405405405407E-2</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="8">
         <f t="shared" si="0"/>
         <v>26.817567567567568</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="15">
         <f t="shared" si="1"/>
         <v>2.0523648648648649</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="8">
         <f>'Revenue by student'!E13</f>
         <v>360</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="8">
         <f t="shared" si="2"/>
         <v>333.18243243243245</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="15">
         <f>'Revenue by student'!D13+E17</f>
         <v>6.5523648648648649</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="20" t="str">
+    <row r="18" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A18" s="7" t="str">
         <f>'Revenue by student'!A14</f>
         <v>Student 11</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="11">
         <f>'Revenue by student'!C14</f>
         <v>9</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="12">
         <f>IFERROR(B18/'Revenue by student'!$C$41,0)</f>
         <v>3.0405405405405407E-2</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="8">
         <f t="shared" si="0"/>
         <v>26.817567567567568</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="15">
         <f t="shared" si="1"/>
         <v>2.0523648648648649</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="8">
         <f>'Revenue by student'!E14</f>
         <v>360</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="8">
         <f t="shared" si="2"/>
         <v>333.18243243243245</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="15">
         <f>'Revenue by student'!D14+E18</f>
         <v>6.5523648648648649</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="20" t="str">
+    <row r="19" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A19" s="7" t="str">
         <f>'Revenue by student'!A15</f>
         <v>Student 12</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="11">
         <f>'Revenue by student'!C15</f>
         <v>7</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="12">
         <f>IFERROR(B19/'Revenue by student'!$C$41,0)</f>
         <v>2.364864864864865E-2</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="8">
         <f t="shared" si="0"/>
         <v>20.858108108108109</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="15">
         <f t="shared" si="1"/>
         <v>1.5962837837837838</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="8">
         <f>'Revenue by student'!E15</f>
         <v>280</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="8">
         <f t="shared" si="2"/>
         <v>259.14189189189187</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="15">
         <f>'Revenue by student'!D15+E19</f>
         <v>5.0962837837837842</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="20" t="str">
+    <row r="20" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A20" s="7" t="str">
         <f>'Revenue by student'!A16</f>
         <v>Student 13</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="11">
         <f>'Revenue by student'!C16</f>
         <v>9</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="12">
         <f>IFERROR(B20/'Revenue by student'!$C$41,0)</f>
         <v>3.0405405405405407E-2</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="8">
         <f t="shared" si="0"/>
         <v>26.817567567567568</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="15">
         <f t="shared" si="1"/>
         <v>2.0523648648648649</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="8">
         <f>'Revenue by student'!E16</f>
         <v>360</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="8">
         <f t="shared" si="2"/>
         <v>333.18243243243245</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="15">
         <f>'Revenue by student'!D16+E20</f>
         <v>6.5523648648648649</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="20" t="str">
+    <row r="21" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A21" s="7" t="str">
         <f>'Revenue by student'!A17</f>
         <v>Student 14</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="11">
         <f>'Revenue by student'!C17</f>
         <v>8</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="12">
         <f>IFERROR(B21/'Revenue by student'!$C$41,0)</f>
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="8">
         <f t="shared" si="0"/>
         <v>23.837837837837839</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="15">
         <f t="shared" si="1"/>
         <v>1.8243243243243243</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="8">
         <f>'Revenue by student'!E17</f>
         <v>320</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="8">
         <f t="shared" si="2"/>
         <v>296.16216216216219</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="15">
         <f>'Revenue by student'!D17+E21</f>
         <v>5.8243243243243246</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="20" t="str">
+    <row r="22" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A22" s="7" t="str">
         <f>'Revenue by student'!A18</f>
         <v>Student 15</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="11">
         <f>'Revenue by student'!C18</f>
         <v>8</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="12">
         <f>IFERROR(B22/'Revenue by student'!$C$41,0)</f>
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="8">
         <f t="shared" si="0"/>
         <v>23.837837837837839</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="15">
         <f t="shared" si="1"/>
         <v>1.8243243243243243</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="8">
         <f>'Revenue by student'!E18</f>
         <v>320</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="8">
         <f t="shared" si="2"/>
         <v>296.16216216216219</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="15">
         <f>'Revenue by student'!D18+E22</f>
         <v>5.8243243243243246</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="20" t="str">
+    <row r="23" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A23" s="7" t="str">
         <f>'Revenue by student'!A19</f>
         <v>Student 16</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="11">
         <f>'Revenue by student'!C19</f>
         <v>8</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="12">
         <f>IFERROR(B23/'Revenue by student'!$C$41,0)</f>
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="8">
         <f t="shared" si="0"/>
         <v>23.837837837837839</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="15">
         <f t="shared" si="1"/>
         <v>1.8243243243243243</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="8">
         <f>'Revenue by student'!E19</f>
         <v>320</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="8">
         <f t="shared" si="2"/>
         <v>296.16216216216219</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H23" s="15">
         <f>'Revenue by student'!D19+E23</f>
         <v>5.8243243243243246</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="20" t="str">
+    <row r="24" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A24" s="7" t="str">
         <f>'Revenue by student'!A20</f>
         <v>Student 17</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="11">
         <f>'Revenue by student'!C20</f>
         <v>8</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="12">
         <f>IFERROR(B24/'Revenue by student'!$C$41,0)</f>
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="8">
         <f t="shared" si="0"/>
         <v>23.837837837837839</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="15">
         <f t="shared" si="1"/>
         <v>1.8243243243243243</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="8">
         <f>'Revenue by student'!E20</f>
         <v>320</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24" s="8">
         <f t="shared" si="2"/>
         <v>296.16216216216219</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H24" s="15">
         <f>'Revenue by student'!D20+E24</f>
         <v>5.8243243243243246</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="20" t="str">
+    <row r="25" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A25" s="7" t="str">
         <f>'Revenue by student'!A21</f>
         <v>Student 18</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="11">
         <f>'Revenue by student'!C21</f>
         <v>7</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="12">
         <f>IFERROR(B25/'Revenue by student'!$C$41,0)</f>
         <v>2.364864864864865E-2</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="8">
         <f t="shared" si="0"/>
         <v>20.858108108108109</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E25" s="15">
         <f t="shared" si="1"/>
         <v>1.5962837837837838</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="8">
         <f>'Revenue by student'!E21</f>
         <v>280</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G25" s="8">
         <f t="shared" si="2"/>
         <v>259.14189189189187</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="15">
         <f>'Revenue by student'!D21+E25</f>
         <v>5.0962837837837842</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="20" t="str">
+    <row r="26" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A26" s="7" t="str">
         <f>'Revenue by student'!A22</f>
         <v>Student 19</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="11">
         <f>'Revenue by student'!C22</f>
         <v>8</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="12">
         <f>IFERROR(B26/'Revenue by student'!$C$41,0)</f>
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="8">
         <f t="shared" si="0"/>
         <v>23.837837837837839</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E26" s="15">
         <f t="shared" si="1"/>
         <v>1.8243243243243243</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="8">
         <f>'Revenue by student'!E22</f>
         <v>320</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26" s="8">
         <f t="shared" si="2"/>
         <v>296.16216216216219</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H26" s="15">
         <f>'Revenue by student'!D22+E26</f>
         <v>5.8243243243243246</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="20" t="str">
+    <row r="27" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A27" s="7" t="str">
         <f>'Revenue by student'!A23</f>
         <v>Student 20</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="11">
         <f>'Revenue by student'!C23</f>
         <v>5</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="12">
         <f>IFERROR(B27/'Revenue by student'!$C$41,0)</f>
         <v>1.6891891891891893E-2</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="8">
         <f t="shared" si="0"/>
         <v>14.898648648648649</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E27" s="15">
         <f t="shared" si="1"/>
         <v>1.1402027027027029</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="8">
         <f>'Revenue by student'!E23</f>
         <v>200</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="8">
         <f t="shared" si="2"/>
         <v>185.10135135135135</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="15">
         <f>'Revenue by student'!D23+E27</f>
         <v>3.6402027027027026</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="20" t="str">
+    <row r="28" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A28" s="7" t="str">
         <f>'Revenue by student'!A24</f>
         <v>Student 21</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="11">
         <f>'Revenue by student'!C24</f>
         <v>8</v>
       </c>
-      <c r="C28" s="11">
+      <c r="C28" s="12">
         <f>IFERROR(B28/'Revenue by student'!$C$41,0)</f>
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="8">
         <f t="shared" si="0"/>
         <v>23.837837837837839</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="15">
         <f t="shared" si="1"/>
         <v>1.8243243243243243</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="8">
         <f>'Revenue by student'!E24</f>
         <v>320</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28" s="8">
         <f t="shared" si="2"/>
         <v>296.16216216216219</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H28" s="15">
         <f>'Revenue by student'!D24+E28</f>
         <v>5.8243243243243246</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="20" t="str">
+    <row r="29" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A29" s="7" t="str">
         <f>'Revenue by student'!A25</f>
         <v>Student 22</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="11">
         <f>'Revenue by student'!C25</f>
         <v>9</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="12">
         <f>IFERROR(B29/'Revenue by student'!$C$41,0)</f>
         <v>3.0405405405405407E-2</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="8">
         <f t="shared" si="0"/>
         <v>26.817567567567568</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E29" s="15">
         <f t="shared" si="1"/>
         <v>2.0523648648648649</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F29" s="8">
         <f>'Revenue by student'!E25</f>
         <v>360</v>
       </c>
-      <c r="G29" s="7">
+      <c r="G29" s="8">
         <f t="shared" si="2"/>
         <v>333.18243243243245</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H29" s="15">
         <f>'Revenue by student'!D25+E29</f>
         <v>6.5523648648648649</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="20" t="str">
+    <row r="30" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A30" s="7" t="str">
         <f>'Revenue by student'!A26</f>
         <v>Student 23</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="11">
         <f>'Revenue by student'!C26</f>
         <v>9</v>
       </c>
-      <c r="C30" s="11">
+      <c r="C30" s="12">
         <f>IFERROR(B30/'Revenue by student'!$C$41,0)</f>
         <v>3.0405405405405407E-2</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="8">
         <f t="shared" si="0"/>
         <v>26.817567567567568</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30" s="15">
         <f t="shared" si="1"/>
         <v>2.0523648648648649</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30" s="8">
         <f>'Revenue by student'!E26</f>
         <v>360</v>
       </c>
-      <c r="G30" s="7">
+      <c r="G30" s="8">
         <f t="shared" si="2"/>
         <v>333.18243243243245</v>
       </c>
-      <c r="H30" s="14">
+      <c r="H30" s="15">
         <f>'Revenue by student'!D26+E30</f>
         <v>6.5523648648648649</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="20" t="str">
+    <row r="31" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A31" s="7" t="str">
         <f>'Revenue by student'!A27</f>
         <v>Student 24</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="11">
         <f>'Revenue by student'!C27</f>
         <v>9</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="12">
         <f>IFERROR(B31/'Revenue by student'!$C$41,0)</f>
         <v>3.0405405405405407E-2</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="8">
         <f t="shared" si="0"/>
         <v>26.817567567567568</v>
       </c>
-      <c r="E31" s="14">
+      <c r="E31" s="15">
         <f t="shared" si="1"/>
         <v>2.0523648648648649</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="8">
         <f>'Revenue by student'!E27</f>
         <v>360</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G31" s="8">
         <f t="shared" si="2"/>
         <v>333.18243243243245</v>
       </c>
-      <c r="H31" s="14">
+      <c r="H31" s="15">
         <f>'Revenue by student'!D27+E31</f>
         <v>6.5523648648648649</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="20" t="str">
+    <row r="32" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A32" s="7" t="str">
         <f>'Revenue by student'!A28</f>
         <v>Student 25</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="11">
         <f>'Revenue by student'!C28</f>
         <v>10</v>
       </c>
-      <c r="C32" s="11">
+      <c r="C32" s="12">
         <f>IFERROR(B32/'Revenue by student'!$C$41,0)</f>
         <v>3.3783783783783786E-2</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="8">
         <f t="shared" si="0"/>
         <v>29.797297297297298</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32" s="15">
         <f t="shared" si="1"/>
         <v>2.2804054054054057</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="8">
         <f>'Revenue by student'!E28</f>
         <v>400</v>
       </c>
-      <c r="G32" s="7">
+      <c r="G32" s="8">
         <f t="shared" si="2"/>
         <v>370.20270270270271</v>
       </c>
-      <c r="H32" s="14">
+      <c r="H32" s="15">
         <f>'Revenue by student'!D28+E32</f>
         <v>7.2804054054054053</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="20" t="str">
+    <row r="33" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A33" s="7" t="str">
         <f>'Revenue by student'!A29</f>
         <v>Student 26</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="11">
         <f>'Revenue by student'!C29</f>
         <v>8</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="12">
         <f>IFERROR(B33/'Revenue by student'!$C$41,0)</f>
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="8">
         <f t="shared" si="0"/>
         <v>23.837837837837839</v>
       </c>
-      <c r="E33" s="14">
+      <c r="E33" s="15">
         <f t="shared" si="1"/>
         <v>1.8243243243243243</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F33" s="8">
         <f>'Revenue by student'!E29</f>
         <v>320</v>
       </c>
-      <c r="G33" s="7">
+      <c r="G33" s="8">
         <f t="shared" si="2"/>
         <v>296.16216216216219</v>
       </c>
-      <c r="H33" s="14">
+      <c r="H33" s="15">
         <f>'Revenue by student'!D29+E33</f>
         <v>5.8243243243243246</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="20" t="str">
+    <row r="34" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A34" s="7" t="str">
         <f>'Revenue by student'!A30</f>
         <v>Student 27</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="11">
         <f>'Revenue by student'!C30</f>
         <v>10</v>
       </c>
-      <c r="C34" s="11">
+      <c r="C34" s="12">
         <f>IFERROR(B34/'Revenue by student'!$C$41,0)</f>
         <v>3.3783783783783786E-2</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="8">
         <f t="shared" si="0"/>
         <v>29.797297297297298</v>
       </c>
-      <c r="E34" s="14">
+      <c r="E34" s="15">
         <f t="shared" si="1"/>
         <v>2.2804054054054057</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F34" s="8">
         <f>'Revenue by student'!E30</f>
         <v>400</v>
       </c>
-      <c r="G34" s="7">
+      <c r="G34" s="8">
         <f t="shared" si="2"/>
         <v>370.20270270270271</v>
       </c>
-      <c r="H34" s="14">
+      <c r="H34" s="15">
         <f>'Revenue by student'!D30+E34</f>
         <v>7.2804054054054053</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="20" t="str">
+    <row r="35" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A35" s="7" t="str">
         <f>'Revenue by student'!A31</f>
         <v>Student 28</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="11">
         <f>'Revenue by student'!C31</f>
         <v>9</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="12">
         <f>IFERROR(B35/'Revenue by student'!$C$41,0)</f>
         <v>3.0405405405405407E-2</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="8">
         <f t="shared" si="0"/>
         <v>26.817567567567568</v>
       </c>
-      <c r="E35" s="14">
+      <c r="E35" s="15">
         <f t="shared" si="1"/>
         <v>2.0523648648648649</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="8">
         <f>'Revenue by student'!E31</f>
         <v>360</v>
       </c>
-      <c r="G35" s="7">
+      <c r="G35" s="8">
         <f t="shared" si="2"/>
         <v>333.18243243243245</v>
       </c>
-      <c r="H35" s="14">
+      <c r="H35" s="15">
         <f>'Revenue by student'!D31+E35</f>
         <v>6.5523648648648649</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="20" t="str">
+    <row r="36" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A36" s="7" t="str">
         <f>'Revenue by student'!A32</f>
         <v>Student 29</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="11">
         <f>'Revenue by student'!C32</f>
         <v>10</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="12">
         <f>IFERROR(B36/'Revenue by student'!$C$41,0)</f>
         <v>3.3783783783783786E-2</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="8">
         <f t="shared" si="0"/>
         <v>29.797297297297298</v>
       </c>
-      <c r="E36" s="14">
+      <c r="E36" s="15">
         <f t="shared" si="1"/>
         <v>2.2804054054054057</v>
       </c>
-      <c r="F36" s="7">
+      <c r="F36" s="8">
         <f>'Revenue by student'!E32</f>
         <v>400</v>
       </c>
-      <c r="G36" s="7">
+      <c r="G36" s="8">
         <f t="shared" si="2"/>
         <v>370.20270270270271</v>
       </c>
-      <c r="H36" s="14">
+      <c r="H36" s="15">
         <f>'Revenue by student'!D32+E36</f>
         <v>7.2804054054054053</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="20" t="str">
+    <row r="37" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A37" s="7" t="str">
         <f>'Revenue by student'!A33</f>
         <v>Student 30</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="11">
         <f>'Revenue by student'!C33</f>
         <v>8</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="12">
         <f>IFERROR(B37/'Revenue by student'!$C$41,0)</f>
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="8">
         <f t="shared" si="0"/>
         <v>23.837837837837839</v>
       </c>
-      <c r="E37" s="14">
+      <c r="E37" s="15">
         <f t="shared" si="1"/>
         <v>1.8243243243243243</v>
       </c>
-      <c r="F37" s="7">
+      <c r="F37" s="8">
         <f>'Revenue by student'!E33</f>
         <v>320</v>
       </c>
-      <c r="G37" s="7">
+      <c r="G37" s="8">
         <f t="shared" si="2"/>
         <v>296.16216216216219</v>
       </c>
-      <c r="H37" s="14">
+      <c r="H37" s="15">
         <f>'Revenue by student'!D33+E37</f>
         <v>5.8243243243243246</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="20" t="str">
+    <row r="38" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A38" s="7" t="str">
         <f>'Revenue by student'!A34</f>
         <v>Student 31</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="11">
         <f>'Revenue by student'!C34</f>
         <v>8</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="12">
         <f>IFERROR(B38/'Revenue by student'!$C$41,0)</f>
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="D38" s="7">
+      <c r="D38" s="8">
         <f t="shared" si="0"/>
         <v>23.837837837837839</v>
       </c>
-      <c r="E38" s="14">
+      <c r="E38" s="15">
         <f t="shared" si="1"/>
         <v>1.8243243243243243</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F38" s="8">
         <f>'Revenue by student'!E34</f>
         <v>320</v>
       </c>
-      <c r="G38" s="7">
+      <c r="G38" s="8">
         <f t="shared" si="2"/>
         <v>296.16216216216219</v>
       </c>
-      <c r="H38" s="14">
+      <c r="H38" s="15">
         <f>'Revenue by student'!D34+E38</f>
         <v>5.8243243243243246</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="20" t="str">
+    <row r="39" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A39" s="7" t="str">
         <f>'Revenue by student'!A35</f>
         <v>Student 32</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="11">
         <f>'Revenue by student'!C35</f>
         <v>8</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="12">
         <f>IFERROR(B39/'Revenue by student'!$C$41,0)</f>
         <v>2.7027027027027029E-2</v>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="8">
         <f t="shared" si="0"/>
         <v>23.837837837837839</v>
       </c>
-      <c r="E39" s="14">
+      <c r="E39" s="15">
         <f t="shared" si="1"/>
         <v>1.8243243243243243</v>
       </c>
-      <c r="F39" s="7">
+      <c r="F39" s="8">
         <f>'Revenue by student'!E35</f>
         <v>320</v>
       </c>
-      <c r="G39" s="7">
+      <c r="G39" s="8">
         <f t="shared" si="2"/>
         <v>296.16216216216219</v>
       </c>
-      <c r="H39" s="14">
+      <c r="H39" s="15">
         <f>'Revenue by student'!D35+E39</f>
         <v>5.8243243243243246</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="20" t="str">
+    <row r="40" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A40" s="7" t="str">
         <f>'Revenue by student'!A36</f>
         <v>Student 33</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B40" s="11">
         <f>'Revenue by student'!C36</f>
         <v>6</v>
       </c>
-      <c r="C40" s="11">
+      <c r="C40" s="12">
         <f>IFERROR(B40/'Revenue by student'!$C$41,0)</f>
         <v>2.0270270270270271E-2</v>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="8">
         <f t="shared" si="0"/>
         <v>17.878378378378379</v>
       </c>
-      <c r="E40" s="14">
+      <c r="E40" s="15">
         <f t="shared" si="1"/>
         <v>1.3682432432432434</v>
       </c>
-      <c r="F40" s="7">
+      <c r="F40" s="8">
         <f>'Revenue by student'!E36</f>
         <v>240</v>
       </c>
-      <c r="G40" s="7">
+      <c r="G40" s="8">
         <f t="shared" si="2"/>
         <v>222.12162162162161</v>
       </c>
-      <c r="H40" s="14">
+      <c r="H40" s="15">
         <f>'Revenue by student'!D36+E40</f>
         <v>4.3682432432432439</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="20" t="str">
+    <row r="41" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A41" s="7" t="str">
         <f>'Revenue by student'!A37</f>
         <v>Student 34</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="11">
         <f>'Revenue by student'!C37</f>
         <v>6</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="12">
         <f>IFERROR(B41/'Revenue by student'!$C$41,0)</f>
         <v>2.0270270270270271E-2</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="8">
         <f t="shared" si="0"/>
         <v>17.878378378378379</v>
       </c>
-      <c r="E41" s="14">
+      <c r="E41" s="15">
         <f t="shared" si="1"/>
         <v>1.3682432432432434</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F41" s="8">
         <f>'Revenue by student'!E37</f>
         <v>240</v>
       </c>
-      <c r="G41" s="7">
+      <c r="G41" s="8">
         <f t="shared" si="2"/>
         <v>222.12162162162161</v>
       </c>
-      <c r="H41" s="14">
+      <c r="H41" s="15">
         <f>'Revenue by student'!D37+E41</f>
         <v>4.3682432432432439</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="20" t="str">
+    <row r="42" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A42" s="7" t="str">
         <f>'Revenue by student'!A38</f>
         <v>Student 35</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B42" s="11">
         <f>'Revenue by student'!C38</f>
         <v>6</v>
       </c>
-      <c r="C42" s="11">
+      <c r="C42" s="12">
         <f>IFERROR(B42/'Revenue by student'!$C$41,0)</f>
         <v>2.0270270270270271E-2</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="8">
         <f t="shared" si="0"/>
         <v>17.878378378378379</v>
       </c>
-      <c r="E42" s="14">
+      <c r="E42" s="15">
         <f t="shared" si="1"/>
         <v>1.3682432432432434</v>
       </c>
-      <c r="F42" s="7">
+      <c r="F42" s="8">
         <f>'Revenue by student'!E38</f>
         <v>240</v>
       </c>
-      <c r="G42" s="7">
+      <c r="G42" s="8">
         <f t="shared" si="2"/>
         <v>222.12162162162161</v>
       </c>
-      <c r="H42" s="14">
+      <c r="H42" s="15">
         <f>'Revenue by student'!D38+E42</f>
         <v>4.3682432432432439</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="20" t="str">
+    <row r="43" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A43" s="7" t="str">
         <f>'Revenue by student'!A39</f>
         <v>Student 36</v>
       </c>
-      <c r="B43" s="10">
+      <c r="B43" s="11">
         <f>'Revenue by student'!C39</f>
         <v>6</v>
       </c>
-      <c r="C43" s="11">
+      <c r="C43" s="12">
         <f>IFERROR(B43/'Revenue by student'!$C$41,0)</f>
         <v>2.0270270270270271E-2</v>
       </c>
-      <c r="D43" s="7">
+      <c r="D43" s="8">
         <f t="shared" si="0"/>
         <v>17.878378378378379</v>
       </c>
-      <c r="E43" s="14">
+      <c r="E43" s="15">
         <f t="shared" si="1"/>
         <v>1.3682432432432434</v>
       </c>
-      <c r="F43" s="7">
+      <c r="F43" s="8">
         <f>'Revenue by student'!E39</f>
         <v>240</v>
       </c>
-      <c r="G43" s="7">
+      <c r="G43" s="8">
         <f t="shared" si="2"/>
         <v>222.12162162162161</v>
       </c>
-      <c r="H43" s="14">
+      <c r="H43" s="15">
         <f>'Revenue by student'!D39+E43</f>
         <v>4.3682432432432439</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="20" t="str">
+    <row r="44" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A44" s="7" t="str">
         <f>'Revenue by student'!A40</f>
         <v>Student 37</v>
       </c>
-      <c r="B44" s="10">
+      <c r="B44" s="11">
         <f>'Revenue by student'!C40</f>
         <v>6</v>
       </c>
-      <c r="C44" s="11">
+      <c r="C44" s="12">
         <f>IFERROR(B44/'Revenue by student'!$C$41,0)</f>
         <v>2.0270270270270271E-2</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D44" s="8">
         <f t="shared" si="0"/>
         <v>17.878378378378379</v>
       </c>
-      <c r="E44" s="14">
+      <c r="E44" s="15">
         <f t="shared" si="1"/>
         <v>1.3682432432432434</v>
       </c>
-      <c r="F44" s="7">
+      <c r="F44" s="8">
         <f>'Revenue by student'!E40</f>
         <v>240</v>
       </c>
-      <c r="G44" s="7">
+      <c r="G44" s="8">
         <f t="shared" si="2"/>
         <v>222.12162162162161</v>
       </c>
-      <c r="H44" s="14">
+      <c r="H44" s="15">
         <f>'Revenue by student'!D40+E44</f>
         <v>4.3682432432432439</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="21" t="s">
+    <row r="45" spans="1:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A45" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="B45" s="23">
+      <c r="B45" s="22">
         <f>SUM(B8:B44)</f>
         <v>296</v>
       </c>
-      <c r="D45" s="24">
+      <c r="D45" s="23">
         <f>SUM(D8:D44)</f>
         <v>881.99999999999966</v>
       </c>
-      <c r="E45" s="23">
+      <c r="E45" s="22">
         <f>SUM(E8:E44)</f>
         <v>67.499999999999957</v>
       </c>
-      <c r="F45" s="24">
+      <c r="F45" s="23">
         <f>SUM(F8:F44)</f>
         <v>11840</v>
       </c>
-      <c r="G45" s="24">
+      <c r="G45" s="23">
         <f>SUM(G8:G44)</f>
         <v>10958.000000000002</v>
       </c>
-      <c r="H45" s="23">
+      <c r="H45" s="22">
         <f>SUM(H8:H44)</f>
         <v>215.50000000000011</v>
       </c>
@@ -9940,143 +9954,143 @@
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:3" ht="23.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="35" t="s">
         <v>198</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
     </row>
     <row r="2" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="34" t="s">
         <v>199</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+    </row>
+    <row r="4" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A4" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="11">
         <f>Assumptions!$B$20</f>
         <v>37</v>
       </c>
-      <c r="C4" s="9"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="C4" s="10"/>
+    </row>
+    <row r="5" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A5" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="13">
         <f>Assumptions!$B$21</f>
         <v>18.5</v>
       </c>
-      <c r="C5" s="9"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="C5" s="10"/>
+    </row>
+    <row r="6" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A6" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="13">
         <f>Assumptions!$B$25</f>
         <v>7.5</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="10" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:3" ht="33.6" x14ac:dyDescent="0.4">
+      <c r="A7" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="13">
         <f>B5+B6</f>
         <v>26</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="10" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A9" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="15">
         <f>'Revenue by student'!$D$41/Assumptions!$B$17</f>
         <v>16.444444444444443</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="10" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A10" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="15">
         <f>'Revenue by student'!$C$41/Assumptions!$B$17</f>
         <v>32.888888888888886</v>
       </c>
-      <c r="C10" s="9"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="C10" s="10"/>
+    </row>
+    <row r="11" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A11" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="12">
         <f>IFERROR(B9/B5,0)</f>
         <v>0.88888888888888884</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="10" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
+    <row r="13" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A13" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="15">
         <f>'Revenue by student'!$B$41/Assumptions!$B$17</f>
         <v>37</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="10" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:3" ht="50.4" x14ac:dyDescent="0.4">
+      <c r="A14" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="12">
         <f>IFERROR(B10/B13,0)</f>
         <v>0.88888888888888884</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="10" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A16" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="8">
         <f>B5*Assumptions!$B$18*Assumptions!$B$9</f>
         <v>53280</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="10" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
+    <row r="17" spans="1:3" ht="33.6" x14ac:dyDescent="0.4">
+      <c r="A17" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="8">
         <f>'Revenue by student'!$E$41/Assumptions!$B$17*Assumptions!$B$18</f>
         <v>47360</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="10" t="s">
         <v>216</v>
       </c>
     </row>
@@ -10099,175 +10113,175 @@
     <col min="3" max="3" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:3" ht="23.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="35" t="s">
         <v>217</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="36" t="s">
         <v>218</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="35"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="B3" s="38"/>
+      <c r="C3" s="37"/>
+    </row>
+    <row r="4" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A4" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="8">
         <f>'Revenue by student'!$E$41</f>
         <v>11840</v>
       </c>
-      <c r="C4" s="9"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="C4" s="10"/>
+    </row>
+    <row r="5" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A5" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="8">
         <f>-'Cost to serve'!$D$45</f>
         <v>-881.99999999999966</v>
       </c>
-      <c r="C5" s="9"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
+      <c r="C5" s="10"/>
+    </row>
+    <row r="6" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A6" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="26">
         <f>B4+B5</f>
         <v>10958</v>
       </c>
-      <c r="C6" s="9"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="C6" s="10"/>
+    </row>
+    <row r="7" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A7" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="8">
         <f>B6*Assumptions!$B$12</f>
         <v>1369.75</v>
       </c>
-      <c r="C7" s="9"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="C7" s="10"/>
+    </row>
+    <row r="8" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A8" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="8">
         <f>B6-B7</f>
         <v>9588.25</v>
       </c>
-      <c r="C8" s="9"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="C8" s="10"/>
+    </row>
+    <row r="9" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A9" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="8">
         <f>B8*Assumptions!$B$13</f>
         <v>1917.65</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="10" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="21" t="s">
+    <row r="10" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A10" s="27" t="s">
         <v>226</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="28">
         <f>B6-B7-B9</f>
         <v>7670.6</v>
       </c>
-      <c r="C10" s="9"/>
+      <c r="C10" s="10"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="34" t="s">
+      <c r="A13" s="36" t="s">
         <v>227</v>
       </c>
-      <c r="B13" s="35"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+      <c r="B13" s="37"/>
+    </row>
+    <row r="14" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A14" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="15">
         <f>Assumptions!$B$18/Assumptions!$B$17</f>
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A15" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="8">
         <f t="shared" ref="B15:B21" si="0">B4*$B$14</f>
         <v>47360</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:3" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A16" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="8">
         <f t="shared" si="0"/>
         <v>-3527.9999999999986</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="21" t="s">
+    <row r="17" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A17" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B17" s="26">
         <f t="shared" si="0"/>
         <v>43832</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+    <row r="18" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A18" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="8">
         <f t="shared" si="0"/>
         <v>5479</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
+    <row r="19" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A19" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="8">
         <f t="shared" si="0"/>
         <v>38353</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
+    <row r="20" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A20" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="8">
         <f t="shared" si="0"/>
         <v>7670.6</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="21" t="s">
+    <row r="21" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A21" s="27" t="s">
         <v>229</v>
       </c>
-      <c r="B21" s="24">
+      <c r="B21" s="28">
         <f t="shared" si="0"/>
         <v>30682.400000000001</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="32" t="s">
+      <c r="A23" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="B23" s="30"/>
+      <c r="B23" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -10290,183 +10304,183 @@
     <col min="2" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:4" ht="23.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="35" t="s">
         <v>230</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-    </row>
-    <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5" t="s">
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+    </row>
+    <row r="4" spans="1:4" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A5" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="15">
         <f>Capacity!$B$10</f>
         <v>32.888888888888886</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="15">
         <f>B5*Assumptions!$B$36</f>
         <v>42.755555555555553</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="15">
         <f>B5*Assumptions!$B$38</f>
         <v>27.955555555555552</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A6" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="8">
         <f>Assumptions!$B$7</f>
         <v>40</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="8">
         <f>Assumptions!$B$7</f>
         <v>40</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="8">
         <f>Assumptions!$B$7*Assumptions!$B$37</f>
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
+    <row r="7" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A7" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="26">
         <f>B5*Assumptions!$B$18*B6</f>
         <v>47360</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="26">
         <f>C5*Assumptions!$B$18*C6</f>
         <v>61567.999999999993</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="26">
         <f>D5*Assumptions!$B$18*D6</f>
         <v>50319.999999999993</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A8" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="8">
         <f>Assumptions!$B$32*Assumptions!$B$18</f>
         <v>3528</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <f>Assumptions!$B$32*Assumptions!$B$18</f>
         <v>3528</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="8">
         <f>Assumptions!$B$32*Assumptions!$B$18</f>
         <v>3528</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
+    <row r="9" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A9" s="25" t="s">
         <v>239</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="26">
         <f>B7-B8</f>
         <v>43832</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="26">
         <f>C7-C8</f>
         <v>58039.999999999993</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="26">
         <f>D7-D8</f>
         <v>46791.999999999993</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A10" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="8">
         <f>B9*Assumptions!$B$12</f>
         <v>5479</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <f>C9*Assumptions!$B$12</f>
         <v>7254.9999999999991</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="8">
         <f>D9*Assumptions!$B$12</f>
         <v>5848.9999999999991</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A11" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="8">
         <f>B9-B10</f>
         <v>38353</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="8">
         <f>C9-C10</f>
         <v>50784.999999999993</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="8">
         <f>D9-D10</f>
         <v>40942.999999999993</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A12" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="8">
         <f>B11*Assumptions!$B$13</f>
         <v>7670.6</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="8">
         <f>C11*Assumptions!$B$13</f>
         <v>10157</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="8">
         <f>D11*Assumptions!$B$13</f>
         <v>8188.5999999999985</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="s">
+    <row r="13" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A13" s="27" t="s">
         <v>243</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="28">
         <f>B9-B10-B12</f>
         <v>30682.400000000001</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="28">
         <f>C9-C10-C12</f>
         <v>40627.999999999993</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="28">
         <f>D9-D10-D12</f>
         <v>32754.399999999994</v>
       </c>
@@ -10490,30 +10504,30 @@
     <col min="3" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:7" ht="23.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="35" t="s">
         <v>244</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="34" t="s">
         <v>245</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+    </row>
+    <row r="4" spans="1:7" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
         <v>246</v>
       </c>
       <c r="B4" s="19">
@@ -10521,8 +10535,8 @@
         <v>47360</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="26" t="s">
+    <row r="5" spans="1:7" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A5" s="4" t="s">
         <v>247</v>
       </c>
       <c r="B5" s="19">
@@ -10530,155 +10544,155 @@
         <v>3527.9999999999986</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:7" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A7" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="27">
+      <c r="B7" s="6"/>
+      <c r="C7" s="29">
         <v>0.9</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="29">
         <v>0.95</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="29">
         <v>1</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="29">
         <v>1.05</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="29">
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="37" t="s">
+    <row r="8" spans="1:7" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A8" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="B8" s="28">
+      <c r="B8" s="30">
         <v>0.8</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <f>(($B$4*$B8*C$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>21399.840000000004</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="8">
         <f>(($B$4*$B8*D$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>22725.919999999998</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <f>(($B$4*$B8*E$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>24052</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <f>(($B$4*$B8*F$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>25378.080000000002</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="8">
         <f>(($B$4*$B8*G$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>26704.160000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="30"/>
-      <c r="B9" s="28">
+    <row r="9" spans="1:7" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A9" s="32"/>
+      <c r="B9" s="30">
         <v>0.9</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="8">
         <f>(($B$4*$B9*C$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>24383.52</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="8">
         <f>(($B$4*$B9*D$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>25875.360000000001</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="8">
         <f>(($B$4*$B9*E$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>27367.200000000001</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="8">
         <f>(($B$4*$B9*F$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>28859.040000000005</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="8">
         <f>(($B$4*$B9*G$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>30350.880000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="30"/>
-      <c r="B10" s="28">
+    <row r="10" spans="1:7" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A10" s="32"/>
+      <c r="B10" s="30">
         <v>1</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <f>(($B$4*$B10*C$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>27367.200000000001</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="8">
         <f>(($B$4*$B10*D$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>29024.800000000003</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="8">
         <f>(($B$4*$B10*E$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>30682.400000000001</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="8">
         <f>(($B$4*$B10*F$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>32340</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="8">
         <f>(($B$4*$B10*G$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>33997.600000000006</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="30"/>
-      <c r="B11" s="28">
+    <row r="11" spans="1:7" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A11" s="32"/>
+      <c r="B11" s="30">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="8">
         <f>(($B$4*$B11*C$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>30350.880000000005</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="8">
         <f>(($B$4*$B11*D$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>32174.240000000005</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <f>(($B$4*$B11*E$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>33997.600000000006</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="8">
         <f>(($B$4*$B11*F$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>35820.960000000014</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="8">
         <f>(($B$4*$B11*G$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>37644.320000000007</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="30"/>
-      <c r="B12" s="28">
+    <row r="12" spans="1:7" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A12" s="32"/>
+      <c r="B12" s="30">
         <v>1.2</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="8">
         <f>(($B$4*$B12*C$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>33334.560000000005</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="8">
         <f>(($B$4*$B12*D$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>35323.679999999993</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="8">
         <f>(($B$4*$B12*E$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>37312.800000000003</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="8">
         <f>(($B$4*$B12*F$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>39301.920000000013</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="8">
         <f>(($B$4*$B12*G$7)-$B$5)*(1-Assumptions!$B$12)*(1-Assumptions!$B$13)</f>
         <v>41291.040000000008</v>
       </c>
